--- a/resumen_semanal_clima.xlsx
+++ b/resumen_semanal_clima.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Windows\Desktop\uflo\ResumenSemanaldelClima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52807DAF-2227-4287-AF04-ED8BD85903AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171C2A96-3A74-4D48-A1CE-1D4667F0E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resumen semanal" sheetId="1" r:id="rId1"/>
     <sheet name="Descripción" sheetId="2" r:id="rId2"/>
-    <sheet name="Gráficos" sheetId="3" r:id="rId3"/>
-    <sheet name="Acumulados 60d" sheetId="4" r:id="rId4"/>
-    <sheet name="Comparativa 60d" sheetId="5" r:id="rId5"/>
-    <sheet name="Gráfico1" sheetId="7" r:id="rId6"/>
-    <sheet name="Hoja1" sheetId="6" r:id="rId7"/>
+    <sheet name="Gráficos" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="Acumulados 60d" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet name="Comparativa 60d" sheetId="7" r:id="rId5"/>
+    <sheet name="calculo crecimiento pasto" sheetId="5" r:id="rId6"/>
+    <sheet name="grafico agua . luz" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="41">
   <si>
     <t>Semana</t>
   </si>
@@ -171,16 +171,19 @@
     <t>Cantidad de días con radiación solar registrada (mayor a 0 W/m²)</t>
   </si>
   <si>
-    <t>HDD escalado a precipitacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fracc precip </t>
+    <t>fracc precipitacion</t>
   </si>
   <si>
     <t>fracc radiacion</t>
   </si>
   <si>
-    <t>agua luz</t>
+    <t>agua*luz</t>
+  </si>
+  <si>
+    <t>max precipitacion</t>
+  </si>
+  <si>
+    <t>max radiacion</t>
   </si>
 </sst>
 </file>
@@ -188,9 +191,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -203,13 +206,30 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF66"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -242,21 +262,27 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -291,6 +317,35 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CO"/>
+              <a:t>grafico</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-CO" baseline="0"/>
+              <a:t> agua * luz</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -331,11 +386,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Hoja1!$F$1</c:f>
+              <c:f>'calculo crecimiento pasto'!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>fracc precip </c:v>
+                  <c:v>fracc precipitacion</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -354,7 +409,7 @@
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln w="22225">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -364,10 +419,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja1!$A$2:$A$155</c:f>
+              <c:f>'calculo crecimiento pasto'!$A$2:$A$157</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm:ss</c:formatCode>
-                <c:ptCount val="154"/>
+                <c:ptCount val="156"/>
                 <c:pt idx="0">
                   <c:v>44760</c:v>
                 </c:pt>
@@ -829,477 +884,489 @@
                 </c:pt>
                 <c:pt idx="153">
                   <c:v>45859</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>45866</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>45873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja1!$F$2:$F$155</c:f>
+              <c:f>'calculo crecimiento pasto'!$I$2:$I$157</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="154"/>
+                <c:ptCount val="156"/>
                 <c:pt idx="0">
-                  <c:v>6.1486486486486483E-2</c:v>
+                  <c:v>6.1429415239220318E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.16655405405405405</c:v>
+                  <c:v>0.16639945996118471</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.26199324324324325</c:v>
+                  <c:v>0.2617500632857987</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.38378378378378375</c:v>
+                  <c:v>0.38342755885579277</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.42905405405405406</c:v>
+                  <c:v>0.42865580963631766</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.47255067567567566</c:v>
+                  <c:v>0.47211205805417267</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.53673986486486491</c:v>
+                  <c:v>0.53624166736984225</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.53673986486486491</c:v>
+                  <c:v>0.53624166736984225</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.5903716216216216</c:v>
+                  <c:v>0.58982364357438199</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.66452702702702704</c:v>
+                  <c:v>0.66391021854695809</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.63893581081081086</c:v>
+                  <c:v>0.63834275588557932</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.68158783783783783</c:v>
+                  <c:v>0.68095519365454393</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.68158783783783783</c:v>
+                  <c:v>0.68095519365454393</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.61604729729729724</c:v>
+                  <c:v>0.61547548730064972</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.65760135135135134</c:v>
+                  <c:v>0.65699097122605699</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.65565878378378373</c:v>
+                  <c:v>0.65505020673360903</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.67947635135135132</c:v>
+                  <c:v>0.67884566703231797</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.77373310810810814</c:v>
+                  <c:v>0.77301493544848543</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.68572635135135129</c:v>
+                  <c:v>0.68508986583410691</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.62043918918918917</c:v>
+                  <c:v>0.61986330267487988</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.55726351351351344</c:v>
+                  <c:v>0.5567462661378787</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.51478040540540537</c:v>
+                  <c:v>0.51430259049869209</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.43505067567567568</c:v>
+                  <c:v>0.43464686524343943</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.36765202702702704</c:v>
+                  <c:v>0.36731077546198637</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.32195945945945947</c:v>
+                  <c:v>0.32166061935701629</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.46081081081081082</c:v>
+                  <c:v>0.46038309003459627</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.49797297297297299</c:v>
+                  <c:v>0.49751075858577343</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.43125000000000002</c:v>
+                  <c:v>0.43084971732343269</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.3921452702702703</c:v>
+                  <c:v>0.39178128427980763</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.40726351351351353</c:v>
+                  <c:v>0.40688549489494558</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.45447635135135139</c:v>
+                  <c:v>0.45405451016791837</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.51613175675675682</c:v>
+                  <c:v>0.51565268753691673</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.50912162162162156</c:v>
+                  <c:v>0.50864905915112646</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.51258445945945941</c:v>
+                  <c:v>0.51210868281157707</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.35717905405405403</c:v>
+                  <c:v>0.35684752341574549</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.2386824324324324</c:v>
+                  <c:v>0.23846088937642396</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.22702702702702698</c:v>
+                  <c:v>0.22681630242173659</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.27854729729729727</c:v>
+                  <c:v>0.27828875200405034</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.28133445945945945</c:v>
+                  <c:v>0.28107332714538857</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.40506756756756757</c:v>
+                  <c:v>0.40469158720783061</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.37804054054054054</c:v>
+                  <c:v>0.37768964644333819</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.31706081081081078</c:v>
+                  <c:v>0.31676651759345203</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.31157094594594592</c:v>
+                  <c:v>0.31128174837566452</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.27373310810810814</c:v>
+                  <c:v>0.2734790313053751</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.3923141891891892</c:v>
+                  <c:v>0.3919500464095857</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.41300675675675674</c:v>
+                  <c:v>0.41262340730740027</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.43445945945945946</c:v>
+                  <c:v>0.43405619778921611</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.41841216216216215</c:v>
+                  <c:v>0.41802379546029872</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.34467905405405408</c:v>
+                  <c:v>0.34435912581216782</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.34138513513513513</c:v>
+                  <c:v>0.34106826428149523</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.44594594594594594</c:v>
+                  <c:v>0.44553202261412544</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.47880067567567564</c:v>
+                  <c:v>0.47835625685596156</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.45185810810810811</c:v>
+                  <c:v>0.45143869715635815</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.43673986486486488</c:v>
+                  <c:v>0.4363344865412202</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.39890202702702704</c:v>
+                  <c:v>0.39853176947093077</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.40523648648648647</c:v>
+                  <c:v>0.40486034933760867</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.50937500000000002</c:v>
+                  <c:v>0.50890220234579364</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.51241554054054061</c:v>
+                  <c:v>0.51193992068179905</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.45456081081081084</c:v>
+                  <c:v>0.45413889123280743</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.39949324324324326</c:v>
+                  <c:v>0.39912243692515403</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.36782094594594594</c:v>
+                  <c:v>0.36747953759176444</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.35836148648648647</c:v>
+                  <c:v>0.35802885832419207</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.3489864864864865</c:v>
+                  <c:v>0.34866256012150876</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.42846283783783784</c:v>
+                  <c:v>0.4280651421820944</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.44864864864864867</c:v>
+                  <c:v>0.44823221669057473</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.33868243243243246</c:v>
+                  <c:v>0.338368070205046</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.53057432432432439</c:v>
+                  <c:v>0.53008184963294247</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.63597972972972971</c:v>
+                  <c:v>0.63538941861446296</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.64349662162162158</c:v>
+                  <c:v>0.64289933338958738</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.68032094594594594</c:v>
+                  <c:v>0.67968947768120835</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.59991554054054053</c:v>
+                  <c:v>0.59935870390684332</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.56486486486486487</c:v>
+                  <c:v>0.56434056197789217</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.44248310810810809</c:v>
+                  <c:v>0.44207239895367478</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.43809121621621627</c:v>
+                  <c:v>0.43768458357944484</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.39805743243243247</c:v>
+                  <c:v>0.39768795882204039</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.31849662162162157</c:v>
+                  <c:v>0.31820099569656568</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.19957770270270273</c:v>
+                  <c:v>0.19939245633279895</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.2189189189189189</c:v>
+                  <c:v>0.21871572019238883</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.18243243243243243</c:v>
+                  <c:v>0.18226310016032404</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.18243243243243243</c:v>
+                  <c:v>0.18226310016032404</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.21444256756756752</c:v>
+                  <c:v>0.21424352375326974</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.27905405405405403</c:v>
+                  <c:v>0.27879503839338454</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.18826013513513509</c:v>
+                  <c:v>0.18808539363766769</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.14653716216216217</c:v>
+                  <c:v>0.14640114758248252</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.15160472972972974</c:v>
+                  <c:v>0.15146401147582483</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.12922297297297297</c:v>
+                  <c:v>0.12910302928022951</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.12550675675675677</c:v>
+                  <c:v>0.12539026242511181</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.13108108108108107</c:v>
+                  <c:v>0.13095941270778838</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.13547297297297298</c:v>
+                  <c:v>0.13534722808201841</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>6.3682432432432434E-2</c:v>
+                  <c:v>6.3623322926335338E-2</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>6.3682432432432434E-2</c:v>
+                  <c:v>6.3623322926335338E-2</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.14417229729729727</c:v>
+                  <c:v>0.1440384777655894</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.20185810810810811</c:v>
+                  <c:v>0.20167074508480298</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.29847972972972969</c:v>
+                  <c:v>0.29820268331786348</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.44070945945945944</c:v>
+                  <c:v>0.44030039659100495</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.46798986486486488</c:v>
+                  <c:v>0.4675554805501646</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.47846283783783783</c:v>
+                  <c:v>0.47801873259640543</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.546875</c:v>
+                  <c:v>0.54636739515652688</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.60278716216216222</c:v>
+                  <c:v>0.60222766011307072</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.68184121621621618</c:v>
+                  <c:v>0.681208336849211</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.66967905405405403</c:v>
+                  <c:v>0.66905746350518946</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.60371621621621618</c:v>
+                  <c:v>0.60315585182685005</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.58885135135135136</c:v>
+                  <c:v>0.58830478440637934</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.52322635135135132</c:v>
+                  <c:v>0.52274069698759607</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.44712837837837838</c:v>
+                  <c:v>0.44671335752257196</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.43395270270270264</c:v>
+                  <c:v>0.43354991139988186</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.32060810810810808</c:v>
+                  <c:v>0.3203105223187917</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.28082770270270269</c:v>
+                  <c:v>0.28056704075605438</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.22483108108108107</c:v>
+                  <c:v>0.22462239473462151</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.10608108108108108</c:v>
+                  <c:v>0.10598261750063286</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.15532094594594595</c:v>
+                  <c:v>0.15517677833094257</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.16613175675675676</c:v>
+                  <c:v>0.16597755463673952</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.25853040540540539</c:v>
+                  <c:v>0.25829043962534809</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.28420608108108103</c:v>
+                  <c:v>0.28394228335161592</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.41824324324324325</c:v>
+                  <c:v>0.41785503333052065</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.47829391891891887</c:v>
+                  <c:v>0.47784997046662731</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.57981418918918914</c:v>
+                  <c:v>0.57927601046325206</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.65396959459459458</c:v>
+                  <c:v>0.65336258543582826</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.8904560810810811</c:v>
+                  <c:v>0.88962956712513719</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.79636824324324318</c:v>
+                  <c:v>0.79562906083874785</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.68167229729729728</c:v>
+                  <c:v>0.68103957471943299</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.66055743243243248</c:v>
+                  <c:v>0.65994430849717334</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.61317567567567566</c:v>
+                  <c:v>0.61260653109442242</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.57913851351351353</c:v>
+                  <c:v>0.57860096194413979</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.51655405405405408</c:v>
+                  <c:v>0.51607459286136192</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.45168918918918916</c:v>
+                  <c:v>0.45126993502658003</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.25599662162162157</c:v>
+                  <c:v>0.25575900767867693</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.11275337837837837</c:v>
+                  <c:v>0.11264872162686694</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.10903716216216215</c:v>
+                  <c:v>0.10893595477174922</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.20135135135135135</c:v>
+                  <c:v>0.20116445869546876</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.35532094594594593</c:v>
+                  <c:v>0.35499113998818665</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.38505067567567564</c:v>
+                  <c:v>0.38469327482912835</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.33682432432432435</c:v>
+                  <c:v>0.33651168677748716</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.42077702702702702</c:v>
+                  <c:v>0.42038646527719181</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.51469594594594592</c:v>
+                  <c:v>0.51421820943380303</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.58369932432432436</c:v>
+                  <c:v>0.58315753944814785</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.64940878378378375</c:v>
+                  <c:v>0.64880600793182008</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.67736486486486491</c:v>
+                  <c:v>0.676736140410092</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.65194256756756752</c:v>
+                  <c:v>0.65133743987849124</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.5868243243243243</c:v>
+                  <c:v>0.58627963884904233</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.91528716216216222</c:v>
+                  <c:v>0.91443760020251463</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>1.0009290540540541</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.88581081081081081</c:v>
+                  <c:v>0.88498860855624006</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.8439189189189189</c:v>
+                  <c:v>0.84313560037127677</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.89957770270270265</c:v>
+                  <c:v>0.89874272213315332</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.85152027027027033</c:v>
+                  <c:v>0.85072989621129025</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.72415540540540535</c:v>
+                  <c:v>0.7234832503586196</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.80540540540540539</c:v>
+                  <c:v>0.80465783478187503</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.73699324324324322</c:v>
+                  <c:v>0.73630917222175352</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.53158783783783781</c:v>
+                  <c:v>0.53109442241161087</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.47483108108108113</c:v>
+                  <c:v>0.47439034680617675</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.47972972972972971</c:v>
+                  <c:v>0.47928444856974101</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.3904560810810811</c:v>
+                  <c:v>0.39009366298202686</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.40937499999999999</c:v>
+                  <c:v>0.39397519196692266</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.43253733862121346</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.51928107332714546</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,7 +1374,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8DF5-4BCC-B342-D534AA3BE3B3}"/>
+              <c16:uniqueId val="{00000000-4218-4947-B79A-904317637AD2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1316,7 +1383,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Hoja1!$G$1</c:f>
+              <c:f>'calculo crecimiento pasto'!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1339,7 +1406,7 @@
               <a:solidFill>
                 <a:schemeClr val="accent2"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln w="22225">
                 <a:solidFill>
                   <a:schemeClr val="accent2"/>
                 </a:solidFill>
@@ -1349,10 +1416,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja1!$A$2:$A$155</c:f>
+              <c:f>'calculo crecimiento pasto'!$A$2:$A$157</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm:ss</c:formatCode>
-                <c:ptCount val="154"/>
+                <c:ptCount val="156"/>
                 <c:pt idx="0">
                   <c:v>44760</c:v>
                 </c:pt>
@@ -1814,477 +1881,489 @@
                 </c:pt>
                 <c:pt idx="153">
                   <c:v>45859</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>45866</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>45873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja1!$G$2:$G$155</c:f>
+              <c:f>'calculo crecimiento pasto'!$J$2:$J$157</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="154"/>
+                <c:ptCount val="156"/>
                 <c:pt idx="0">
-                  <c:v>7.1143115942028989E-2</c:v>
+                  <c:v>7.0954931124698264E-2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0.15050543478260869</c:v>
+                  <c:v>0.15010732405359695</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.22524184782608697</c:v>
+                  <c:v>0.22464604743939984</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.30920018115942033</c:v>
+                  <c:v>0.30838229767428416</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.41492210144927538</c:v>
+                  <c:v>0.41382456672882062</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.50115851449275362</c:v>
+                  <c:v>0.49983287079195748</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.57868478260869571</c:v>
+                  <c:v>0.57715406964138583</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.66341757246376809</c:v>
+                  <c:v>0.66166272783776359</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.71986865942028988</c:v>
+                  <c:v>0.71796449272220053</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.73687499999999995</c:v>
+                  <c:v>0.73492584883569656</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.75473913043478258</c:v>
+                  <c:v>0.75274272581414503</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.75779710144927537</c:v>
+                  <c:v>0.7557926080106383</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.7584157608695653</c:v>
+                  <c:v>0.75640963097870861</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.75104076086956517</c:v>
+                  <c:v>0.74905413902259221</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.7238278985507246</c:v>
+                  <c:v>0.72191325903762482</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.72858786231884054</c:v>
+                  <c:v>0.72666063194715458</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.7365208333333334</c:v>
+                  <c:v>0.73457261899599613</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.73565760869565222</c:v>
+                  <c:v>0.73371167772429635</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.74570471014492756</c:v>
+                  <c:v>0.74373220299784626</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.75464764492753622</c:v>
+                  <c:v>0.75265148230056511</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.73737952898550729</c:v>
+                  <c:v>0.73542904326207303</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.74510054347826082</c:v>
+                  <c:v>0.74312963444776892</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.81463224637681164</c:v>
+                  <c:v>0.81247741497188608</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.8185461956521739</c:v>
+                  <c:v>0.81638101123108264</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.81029710144927536</c:v>
+                  <c:v>0.8081537371897719</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.80638496376811597</c:v>
+                  <c:v>0.80425194773282449</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.78160597826086964</c:v>
+                  <c:v>0.77953850656953294</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.8079184782608696</c:v>
+                  <c:v>0.80578140583669389</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.84210416666666665</c:v>
+                  <c:v>0.8398766676784758</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.86699637681159414</c:v>
+                  <c:v>0.86470303398233661</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.84838677536231888</c:v>
+                  <c:v>0.8461426578783805</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.84112500000000001</c:v>
+                  <c:v>0.83890009106283325</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.83186141304347827</c:v>
+                  <c:v>0.82966100776202234</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.81505163043478257</c:v>
+                  <c:v>0.81289568969255444</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.84075271739130442</c:v>
+                  <c:v>0.83852879320064178</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.83985688405797099</c:v>
+                  <c:v>0.83763532948845809</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.86549275362318845</c:v>
+                  <c:v>0.86320338811557751</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.8290860507246377</c:v>
+                  <c:v>0.82689298671638978</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.79463315217391306</c:v>
+                  <c:v>0.79253122154286448</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.77517028985507253</c:v>
+                  <c:v>0.77311984157957869</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.75854891304347827</c:v>
+                  <c:v>0.75654243094401796</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.75020018115942033</c:v>
+                  <c:v>0.74821578277900636</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.7522771739130435</c:v>
+                  <c:v>0.75028728155760804</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.76377536231884058</c:v>
+                  <c:v>0.76175505543269295</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.72459692028985512</c:v>
+                  <c:v>0.72268024659237096</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.72337228260869557</c:v>
+                  <c:v>0.72145884827197426</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.71682427536231885</c:v>
+                  <c:v>0.71492816154257544</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.7127817028985507</c:v>
+                  <c:v>0.71089628232369206</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.72542028985507245</c:v>
+                  <c:v>0.72350143821459023</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.72235597826086961</c:v>
+                  <c:v>0.72044523221022494</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.69958695652173919</c:v>
+                  <c:v>0.69773643814231823</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.69325090579710147</c:v>
+                  <c:v>0.69141714727606485</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.68957880434782604</c:v>
+                  <c:v>0.68775475911712403</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.69593025362318839</c:v>
+                  <c:v>0.69408940780249473</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.69160416666666658</c:v>
+                  <c:v>0.68977476403162619</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.69346920289855074</c:v>
+                  <c:v>0.69163486694708232</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.69767934782608698</c:v>
+                  <c:v>0.69583387537400809</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.72253442028985504</c:v>
+                  <c:v>0.72062320223176202</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.75148460144927542</c:v>
+                  <c:v>0.74949680557362353</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.76778894927536234</c:v>
+                  <c:v>0.76575802581559049</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.78783061594202897</c:v>
+                  <c:v>0.78574667909746609</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.80738405797101442</c:v>
+                  <c:v>0.80524839917320723</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.83722916666666669</c:v>
+                  <c:v>0.83501456282612774</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.84352173913043482</c:v>
+                  <c:v>0.84129049043840243</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.86010507246376811</c:v>
+                  <c:v>0.85782995822673191</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.85104076086956515</c:v>
+                  <c:v>0.84878962317332285</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.83221286231884062</c:v>
+                  <c:v>0.83001152739834927</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.79769836956521734</c:v>
+                  <c:v>0.79558833094835424</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.79178804347826093</c:v>
+                  <c:v>0.78969363861064124</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.82056702898550715</c:v>
+                  <c:v>0.81839649913996204</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.81099094202898547</c:v>
+                  <c:v>0.80884574245118013</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.81750362318840575</c:v>
+                  <c:v>0.81534119653672132</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.82071648550724641</c:v>
+                  <c:v>0.8185455603255134</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.81291304347826088</c:v>
+                  <c:v>0.81076275963748312</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.81878079710144924</c:v>
+                  <c:v>0.81661499212234212</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.82005525362318843</c:v>
+                  <c:v>0.81788607750458919</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.87923188405797104</c:v>
+                  <c:v>0.87690617637280832</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.91500905797101451</c:v>
+                  <c:v>0.91258871399043107</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.92127083333333326</c:v>
+                  <c:v>0.91883392596447089</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.96749637681159417</c:v>
+                  <c:v>0.96493719555382096</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.96168387681159428</c:v>
+                  <c:v>0.95914007053755979</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.93564945652173925</c:v>
+                  <c:v>0.93317451541563678</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.95266938405797108</c:v>
+                  <c:v>0.9501494225460011</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>1.0026521739130436</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.98495833333333338</c:v>
+                  <c:v>0.98235296243296755</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.94422373188405795</c:v>
+                  <c:v>0.94172611046066224</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.89690489130434781</c:v>
+                  <c:v>0.89453243571397589</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.88394836956521738</c:v>
+                  <c:v>0.8816101860283595</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.85245652173913045</c:v>
+                  <c:v>0.85020163913100022</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>0.84492663043478256</c:v>
+                  <c:v>0.84269166558258524</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>0.8803405797101449</c:v>
+                  <c:v>0.87801193934926203</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.85549547101449275</c:v>
+                  <c:v>0.85323254990387798</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.81015851449275356</c:v>
+                  <c:v>0.80801551681771522</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.78769384057971015</c:v>
+                  <c:v>0.78561026552765845</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.78101539855072466</c:v>
+                  <c:v>0.77894948903632388</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.78025090579710155</c:v>
+                  <c:v>0.77818701848720062</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.73692481884057981</c:v>
+                  <c:v>0.73497553589754705</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.73395471014492752</c:v>
+                  <c:v>0.73201328361013529</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.7191757246376812</c:v>
+                  <c:v>0.71727339086191688</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.62941304347826088</c:v>
+                  <c:v>0.62774814622089237</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.61950724637681165</c:v>
+                  <c:v>0.61786855152277287</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.62078894927536232</c:v>
+                  <c:v>0.61914686411401643</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.6233115942028985</c:v>
+                  <c:v>0.62166283624589846</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.63708514492753621</c:v>
+                  <c:v>0.63539995374586233</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.64803260869565216</c:v>
+                  <c:v>0.64631845973721858</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.63588768115942029</c:v>
+                  <c:v>0.63420565745920232</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.6733324275362319</c:v>
+                  <c:v>0.67155135654712861</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.68613677536231887</c:v>
+                  <c:v>0.68432183484381992</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.74581249999999999</c:v>
+                  <c:v>0.74383970773166808</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>0.79381068840579705</c:v>
+                  <c:v>0.79171093332176967</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.82736050724637678</c:v>
+                  <c:v>0.82517200757411491</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.84706793478260867</c:v>
+                  <c:v>0.84482730584103027</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.85208695652173905</c:v>
+                  <c:v>0.84983305147218235</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.88622826086956519</c:v>
+                  <c:v>0.88388404665886111</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.90317300724637672</c:v>
+                  <c:v>0.90078397149588763</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.89492119565217398</c:v>
+                  <c:v>0.89255398725120327</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.88036322463768124</c:v>
+                  <c:v>0.87803452437737595</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.83278442028985511</c:v>
+                  <c:v>0.83058157350794259</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.81950362318840575</c:v>
+                  <c:v>0.81733590621973595</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.82967844202898555</c:v>
+                  <c:v>0.82748381105184798</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.8412608695652174</c:v>
+                  <c:v>0.83903560123151633</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.84430615942028986</c:v>
+                  <c:v>0.842072835812266</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.81622101449275353</c:v>
+                  <c:v>0.8140619805443533</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.81472101449275358</c:v>
+                  <c:v>0.81256594828209239</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.80549818840579712</c:v>
+                  <c:v>0.80336751803188633</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.84702355072463775</c:v>
+                  <c:v>0.84478303918592712</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.90142300724637681</c:v>
+                  <c:v>0.89903860052324991</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.93241666666666656</c:v>
+                  <c:v>0.9299502768021044</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.93716213768115941</c:v>
+                  <c:v>0.93468319529364141</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.91860144927536225</c:v>
+                  <c:v>0.9161716028504111</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.90345742753623193</c:v>
+                  <c:v>0.90106763944899748</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.89321648550724642</c:v>
+                  <c:v>0.89085378633479317</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.88492119565217386</c:v>
+                  <c:v>0.88258043883613013</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.88699637681159427</c:v>
+                  <c:v>0.88465013081248278</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.84866032608695652</c:v>
+                  <c:v>0.84641548501799568</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.77921376811594201</c:v>
+                  <c:v>0.77715262419958653</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.79377355072463773</c:v>
+                  <c:v>0.791673893875663</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.78300724637681163</c:v>
+                  <c:v>0.78093606810921756</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.7943786231884058</c:v>
+                  <c:v>0.79227736582686492</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.81058514492753619</c:v>
+                  <c:v>0.80844101874738006</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.82074365942028982</c:v>
+                  <c:v>0.81857266235924997</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.81923550724637684</c:v>
+                  <c:v>0.81706849948686811</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.79534510869565223</c:v>
+                  <c:v>0.79324129482676375</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.77807608695652175</c:v>
+                  <c:v>0.77601795238714699</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.75641485507246375</c:v>
+                  <c:v>0.75441401789456941</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.75115398550724632</c:v>
+                  <c:v>0.74916706416316137</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.74334601449275362</c:v>
+                  <c:v>0.74137974646950833</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.70840036231884052</c:v>
+                  <c:v>0.70652653108422581</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.68918025362318847</c:v>
+                  <c:v>0.68735726262232044</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.68825815217391306</c:v>
+                  <c:v>0.68643760027752476</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.68172463768115943</c:v>
+                  <c:v>0.67992136796611879</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.68871829710144927</c:v>
+                  <c:v>0.68689652804879808</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.69643931159420291</c:v>
+                  <c:v>0.69459711923449396</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.69674637681159413</c:v>
+                  <c:v>0.70787892256768281</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.70533584840206398</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.70591854212740113</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2292,7 +2371,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8DF5-4BCC-B342-D534AA3BE3B3}"/>
+              <c16:uniqueId val="{00000001-4218-4947-B79A-904317637AD2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2301,11 +2380,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Hoja1!$H$1</c:f>
+              <c:f>'calculo crecimiento pasto'!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>agua luz</c:v>
+                  <c:v>agua*luz</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2324,7 +2403,7 @@
               <a:solidFill>
                 <a:schemeClr val="accent3"/>
               </a:solidFill>
-              <a:ln w="47625">
+              <a:ln w="22225">
                 <a:solidFill>
                   <a:schemeClr val="accent3"/>
                 </a:solidFill>
@@ -2334,10 +2413,10 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja1!$A$2:$A$155</c:f>
+              <c:f>'calculo crecimiento pasto'!$A$2:$A$157</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd\ hh:mm:ss</c:formatCode>
-                <c:ptCount val="154"/>
+                <c:ptCount val="156"/>
                 <c:pt idx="0">
                   <c:v>44760</c:v>
                 </c:pt>
@@ -2799,477 +2878,489 @@
                 </c:pt>
                 <c:pt idx="153">
                   <c:v>45859</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>45866</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>45873</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja1!$H$2:$H$155</c:f>
+              <c:f>'calculo crecimiento pasto'!$K$2:$K$157</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="154"/>
+                <c:ptCount val="156"/>
                 <c:pt idx="0">
-                  <c:v>4.3743402369761063E-3</c:v>
+                  <c:v>4.3587199273293674E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.5067290320211513E-2</c:v>
+                  <c:v>2.4977777658737085E-2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>5.9011842226057584E-2</c:v>
+                  <c:v>5.8801117134167441E-2</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>0.11866601547199374</c:v>
+                  <c:v>0.11824227159159119</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.1780240097434391</c:v>
+                  <c:v>0.17738830469854097</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.23682279464416861</c:v>
+                  <c:v>0.23597712531271642</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0.31060319201674508</c:v>
+                  <c:v>0.30949406063378676</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>0.35608265819317964</c:v>
+                  <c:v>0.35481112441220047</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.42499002781653938</c:v>
+                  <c:v>0.42347243305444116</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.48967335304054049</c:v>
+                  <c:v>0.48792478091631597</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.48222985825499415</c:v>
+                  <c:v>0.48050786606902435</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.51650528789659222</c:v>
+                  <c:v>0.51466090175055701</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.51692695863322569</c:v>
+                  <c:v>0.51508106674526866</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0.46267663089380134</c:v>
+                  <c:v>0.46102446122949858</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.47599020423276533</c:v>
+                  <c:v>0.47429049319609717</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.47770503168759787</c:v>
+                  <c:v>0.47599919718215861</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.50044848852759016</c:v>
+                  <c:v>0.49866143952601377</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.56920264807946541</c:v>
+                  <c:v>0.56717008519384693</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.51134937007319814</c:v>
+                  <c:v>0.50952339516829925</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.46821297294237169</c:v>
+                  <c:v>0.46654103358197219</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.4109147071154034</c:v>
+                  <c:v>0.40944737384551161</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.38356315983952699</c:v>
+                  <c:v>0.38219349607283365</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.35440630921342542</c:v>
+                  <c:v>0.35314076149862339</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.3009401680467832</c:v>
+                  <c:v>0.29986554230772955</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.26088281678417546</c:v>
+                  <c:v>0.25995123164014938</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.37159090897963182</c:v>
+                  <c:v>0.37026399686358036</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.38921865268801414</c:v>
+                  <c:v>0.38782879375022927</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.34841484375000004</c:v>
+                  <c:v>0.34717069092921776</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.33022716603322072</c:v>
+                  <c:v>0.32904795949971843</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.35309599062377595</c:v>
+                  <c:v>0.35183512191906396</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.38557172620140528</c:v>
+                  <c:v>0.38419489005514862</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.43413132390202708</c:v>
+                  <c:v>0.43258108653151417</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.42351863157314917</c:v>
+                  <c:v>0.42200629101252807</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.41778279941796409</c:v>
+                  <c:v>0.41629094091166252</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.30029926029120152</c:v>
+                  <c:v>0.29922692316644284</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>0.20045908398207987</c:v>
+                  <c:v>0.19974326564293163</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.1964902467685076</c:v>
+                  <c:v>0.1957886007302905</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.23093967865623774</c:v>
+                  <c:v>0.23011501731420589</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.22355768833541423</c:v>
+                  <c:v>0.22275938730565198</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>0.3139963437622405</c:v>
+                  <c:v>0.31287509579070627</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>0.28676224111339599</c:v>
+                  <c:v>0.28573824326262975</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>0.23785907770882295</c:v>
+                  <c:v>0.2370097079193646</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>0.23438771068962982</c:v>
+                  <c:v>0.2335507367872767</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>0.20907060382393264</c:v>
+                  <c:v>0.20832403465170518</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>0.28426965327249809</c:v>
+                  <c:v>0.28325455619117063</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>0.29875764036794944</c:v>
+                  <c:v>0.2976908082060547</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>0.31143108720133178</c:v>
+                  <c:v>0.3103189994916048</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>0.29823653345941048</c:v>
+                  <c:v>0.29717156211556583</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>0.2500371792988641</c:v>
+                  <c:v>0.24914432278742243</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>0.2466015932542597</c:v>
+                  <c:v>0.24572100485982021</c:v>
                 </c:pt>
                 <c:pt idx="50">
-                  <c:v>0.31197796709753234</c:v>
+                  <c:v>0.31086392653712264</c:v>
                 </c:pt>
                 <c:pt idx="51">
-                  <c:v>0.33192900210842635</c:v>
+                  <c:v>0.33074371849700546</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>0.3115917739240599</c:v>
+                  <c:v>0.3104791124189194</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>0.30394048492276243</c:v>
+                  <c:v>0.30285514536720115</c:v>
                 </c:pt>
                 <c:pt idx="54">
-                  <c:v>0.27588230398367114</c:v>
+                  <c:v>0.27489715724591773</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>0.28101902326919309</c:v>
+                  <c:v>0.28001553384626626</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>0.35538041779891305</c:v>
+                  <c:v>0.35411139164464123</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>0.37023786553197224</c:v>
+                  <c:v>0.36891578499199229</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>0.34159544974662165</c:v>
+                  <c:v>0.34037564826573641</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>0.30672649747233649</c:v>
+                  <c:v>0.30563120935851351</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>0.28978060240097431</c:v>
+                  <c:v>0.28874582629900136</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>0.28933535117998427</c:v>
+                  <c:v>0.2883021650233667</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>0.29218166525900902</c:v>
+                  <c:v>0.29113831521370009</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>0.36141771812573442</c:v>
+                  <c:v>0.36012713340595864</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>0.3858849784567176</c:v>
+                  <c:v>0.38450702371955114</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>0.28823255499045242</c:v>
+                  <c:v>0.28720330680322542</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>0.44155077711883084</c:v>
+                  <c:v>0.43997404565998066</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>0.50731999348193302</c:v>
+                  <c:v>0.50550840705772571</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>0.50951293101865458</c:v>
+                  <c:v>0.50769351384477901</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>0.55824893737147463</c:v>
+                  <c:v>0.55625548903657029</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>0.48652606936080101</c:v>
+                  <c:v>0.48478873585610771</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>0.46177907363885623</c:v>
+                  <c:v>0.46013010905726037</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>0.36315318138280944</c:v>
+                  <c:v>0.36185639950597964</c:v>
                 </c:pt>
                 <c:pt idx="73">
-                  <c:v>0.35613006389541718</c:v>
+                  <c:v>0.35485836083365335</c:v>
                 </c:pt>
                 <c:pt idx="74">
-                  <c:v>0.32592178181918335</c:v>
+                  <c:v>0.32475794936061081</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>0.26118482782204755</c:v>
+                  <c:v>0.26025216422831876</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>0.17547507956325895</c:v>
+                  <c:v>0.17484847648037688</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>0.2003127937720329</c:v>
+                  <c:v>0.19959749781986308</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>0.16806967905405404</c:v>
+                  <c:v>0.16746951987876613</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>0.17650271739130433</c:v>
+                  <c:v>0.17587244472164826</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>0.2062259597318106</c:v>
+                  <c:v>0.20548954848492651</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>0.26109677401586373</c:v>
+                  <c:v>0.26016442485303048</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>0.17934966698185956</c:v>
+                  <c:v>0.17870922815416726</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>0.14692580420094009</c:v>
+                  <c:v>0.14640114758248252</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>0.14932434192004507</c:v>
+                  <c:v>0.14879112037525752</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>0.1220153977856933</c:v>
+                  <c:v>0.12157969361275953</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>0.11256762402688014</c:v>
+                  <c:v>0.1121656568619499</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>0.11586890790246768</c:v>
+                  <c:v>0.11545515219947802</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>0.11548481933019977</c:v>
+                  <c:v>0.11507243516716939</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>5.380698305302585E-2</c:v>
+                  <c:v>5.3614843966692208E-2</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>5.60622294849197E-2</c:v>
+                  <c:v>5.5862037150396053E-2</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>0.12333874738359281</c:v>
+                  <c:v>0.12289831766820687</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>0.16353706500318252</c:v>
+                  <c:v>0.16295309131671079</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>0.23511064464600467</c:v>
+                  <c:v>0.23427108922240697</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>0.34420087412480416</c:v>
+                  <c:v>0.34297176894705406</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>0.36514951596467399</c:v>
+                  <c:v>0.36384560538668292</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>0.35259114009559833</c:v>
+                  <c:v>0.35133207415910933</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>0.40138148211050723</c:v>
+                  <c:v>0.39994819098604556</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>0.43350989415026447</c:v>
+                  <c:v>0.43196187584014023</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>0.42915975506756754</c:v>
+                  <c:v>0.42762727064730943</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>0.41487102673325504</c:v>
+                  <c:v>0.41338956586145187</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>0.37478035552536232</c:v>
+                  <c:v>0.37344205423061255</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>0.36703787455934195</c:v>
+                  <c:v>0.3657272208511016</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>0.33333973588058163</c:v>
+                  <c:v>0.33214941468699838</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>0.28975376946239717</c:v>
+                  <c:v>0.28871908917803013</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>0.27594517785448486</c:v>
+                  <c:v>0.27495980660074099</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>0.21587583572023109</c:v>
+                  <c:v>0.21510496577950389</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>0.19268621436484037</c:v>
+                  <c:v>0.19199815212688393</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>0.16768183065878378</c:v>
+                  <c:v>0.16708305644938823</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>8.4208295999804145E-2</c:v>
+                  <c:v>8.3907597017310154E-2</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>0.12850641662382492</c:v>
+                  <c:v>0.12804753370422728</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>0.14072488409775263</c:v>
+                  <c:v>0.14022237031383905</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>0.22029038631022324</c:v>
+                  <c:v>0.21950375247290105</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>0.25187146096504109</c:v>
+                  <c:v>0.25097205442638326</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>0.37774600776047784</c:v>
+                  <c:v>0.37639711643301288</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>0.42803536579208284</c:v>
+                  <c:v>0.42650689644785794</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>0.51044708928527716</c:v>
+                  <c:v>0.50862433633032533</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>0.54461568972165098</c:v>
+                  <c:v>0.54267092428250785</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>0.7297319847360948</c:v>
+                  <c:v>0.72712618844609544</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>0.66072956333541422</c:v>
+                  <c:v>0.65837016744644972</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>0.57346422958284371</c:v>
+                  <c:v>0.5714164490371757</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>0.55771270885355473</c:v>
+                  <c:v>0.5557211753343797</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>0.5004868720622796</c:v>
+                  <c:v>0.49869968599713149</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>0.471836317261555</c:v>
+                  <c:v>0.47015143931907077</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>0.41608335475421077</c:v>
+                  <c:v>0.41459756478634857</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>0.38259138085095967</c:v>
+                  <c:v>0.38122518720499016</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>0.23076124450707497</c:v>
+                  <c:v>0.22993722033465283</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>0.10513312922297295</c:v>
+                  <c:v>0.10475770985830811</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>0.10218549997857911</c:v>
+                  <c:v>0.10182060628842217</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>0.18496164316490402</c:v>
+                  <c:v>0.18430116455956294</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>0.32101734777406482</c:v>
+                  <c:v>0.31987102853446397</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>0.34393361126921757</c:v>
+                  <c:v>0.3427054604590602</c:v>
                 </c:pt>
                 <c:pt idx="132">
-                  <c:v>0.29806298380581669</c:v>
+                  <c:v>0.29699863218956096</c:v>
                 </c:pt>
                 <c:pt idx="133">
-                  <c:v>0.37322769841852727</c:v>
+                  <c:v>0.371894941499265</c:v>
                 </c:pt>
                 <c:pt idx="134">
-                  <c:v>0.43680202932212103</c:v>
+                  <c:v>0.43524225514299769</c:v>
                 </c:pt>
                 <c:pt idx="135">
-                  <c:v>0.45482654995348609</c:v>
+                  <c:v>0.453202412103902</c:v>
                 </c:pt>
                 <c:pt idx="136">
-                  <c:v>0.51548351617582255</c:v>
+                  <c:v>0.5136427786693083</c:v>
                 </c:pt>
                 <c:pt idx="137">
-                  <c:v>0.53038159763023895</c:v>
+                  <c:v>0.52848766063926467</c:v>
                 </c:pt>
                 <c:pt idx="138">
-                  <c:v>0.51788923922223851</c:v>
+                  <c:v>0.51603991113134506</c:v>
                 </c:pt>
                 <c:pt idx="139">
-                  <c:v>0.47567107997943592</c:v>
+                  <c:v>0.47397250850196582</c:v>
                 </c:pt>
                 <c:pt idx="140">
-                  <c:v>0.75121613489338523</c:v>
+                  <c:v>0.74853362095917586</c:v>
                 </c:pt>
                 <c:pt idx="141">
-                  <c:v>0.81999662131560913</c:v>
+                  <c:v>0.81706849948686811</c:v>
                 </c:pt>
                 <c:pt idx="142">
-                  <c:v>0.70452529560810817</c:v>
+                  <c:v>0.70200950975808785</c:v>
                 </c:pt>
                 <c:pt idx="143">
-                  <c:v>0.65663313014101055</c:v>
+                  <c:v>0.654288362184826</c:v>
                 </c:pt>
                 <c:pt idx="144">
-                  <c:v>0.6804539376162847</c:v>
+                  <c:v>0.67802410805797475</c:v>
                 </c:pt>
                 <c:pt idx="145">
-                  <c:v>0.63962284475372111</c:v>
+                  <c:v>0.63733881874044329</c:v>
                 </c:pt>
                 <c:pt idx="146">
-                  <c:v>0.53829803448149227</c:v>
+                  <c:v>0.53637582872580924</c:v>
                 </c:pt>
                 <c:pt idx="147">
-                  <c:v>0.57054948100274183</c:v>
+                  <c:v>0.56851210871818225</c:v>
                 </c:pt>
                 <c:pt idx="148">
-                  <c:v>0.50792119029695459</c:v>
+                  <c:v>0.50610745706205118</c:v>
                 </c:pt>
                 <c:pt idx="149">
-                  <c:v>0.36586966298839602</c:v>
+                  <c:v>0.36456318084100425</c:v>
                 </c:pt>
                 <c:pt idx="150">
-                  <c:v>0.32370404670975328</c:v>
+                  <c:v>0.3225481335503772</c:v>
                 </c:pt>
                 <c:pt idx="151">
-                  <c:v>0.33039864252839796</c:v>
+                  <c:v>0.32921882367033783</c:v>
                 </c:pt>
                 <c:pt idx="152">
-                  <c:v>0.27192896431587837</c:v>
+                  <c:v>0.2709579345389474</c:v>
                 </c:pt>
                 <c:pt idx="153">
-                  <c:v>0.28523054800724634</c:v>
+                  <c:v>0.27888673440794121</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>0.30508409070196441</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>0.3665701382374506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3277,7 +3368,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8DF5-4BCC-B342-D534AA3BE3B3}"/>
+              <c16:uniqueId val="{00000002-4218-4947-B79A-904317637AD2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3289,11 +3380,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="2011340080"/>
-        <c:axId val="2011342000"/>
+        <c:axId val="463885552"/>
+        <c:axId val="463879792"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="2011340080"/>
+        <c:axId val="463885552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3350,12 +3441,12 @@
             <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2011342000"/>
+        <c:crossAx val="463879792"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="2011342000"/>
+        <c:axId val="463879792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -3413,7 +3504,7 @@
             <a:endParaRPr lang="es-CO"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2011340080"/>
+        <c:crossAx val="463885552"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -3458,6 +3549,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3465,7 +3557,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4052,7 +4143,7 @@
 </file>
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{B3A02E06-4929-4234-89DC-6F166880FBDF}">
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{D6A250BB-FD62-417A-B8AA-6E06412827EE}">
   <sheetPr/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -4090,6 +4181,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4123,6 +4217,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4156,6 +4253,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4194,6 +4294,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4227,6 +4330,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4260,6 +4366,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -4282,7 +4391,7 @@
         <xdr:cNvPr id="2" name="Image 1" descr="Picture">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4315,7 +4424,7 @@
         <xdr:cNvPr id="2" name="Gráfico 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DD14F09-E36F-BBCE-C398-8BC48A7C46E2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D48B10E-B77D-ABC7-7ACC-583E093CB57B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4623,62 +4732,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q155"/>
+  <dimension ref="A1:Q157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="16" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
@@ -5285,7 +5395,7 @@
         <v>83.019448946515396</v>
       </c>
       <c r="G13">
-        <v>2.3040518638573748</v>
+        <v>2.3040518638573739</v>
       </c>
       <c r="H13">
         <v>19.8</v>
@@ -5397,7 +5507,7 @@
         <v>30</v>
       </c>
       <c r="I15">
-        <v>137.56521739130429</v>
+        <v>137.13931888544889</v>
       </c>
       <c r="J15">
         <v>15.225</v>
@@ -5662,7 +5772,7 @@
         <v>1.8</v>
       </c>
       <c r="I20">
-        <v>162.26946107784431</v>
+        <v>162.77428998505229</v>
       </c>
       <c r="J20">
         <v>4.375</v>
@@ -5671,10 +5781,10 @@
         <v>202.97499999999999</v>
       </c>
       <c r="L20">
-        <v>27099</v>
+        <v>27224</v>
       </c>
       <c r="M20">
-        <v>205814.5</v>
+        <v>205939.5</v>
       </c>
       <c r="N20">
         <v>605.57500000000005</v>
@@ -5727,7 +5837,7 @@
         <v>27346.25</v>
       </c>
       <c r="M21">
-        <v>208282.75</v>
+        <v>208407.75</v>
       </c>
       <c r="N21">
         <v>549.97500000000002</v>
@@ -5780,7 +5890,7 @@
         <v>21699.5</v>
       </c>
       <c r="M22">
-        <v>203516.75</v>
+        <v>203641.75</v>
       </c>
       <c r="N22">
         <v>523.77499999999998</v>
@@ -5833,7 +5943,7 @@
         <v>25005.75</v>
       </c>
       <c r="M23">
-        <v>205647.75</v>
+        <v>205772.75</v>
       </c>
       <c r="N23">
         <v>391.47500000000002</v>
@@ -5886,7 +5996,7 @@
         <v>34082.75</v>
       </c>
       <c r="M24">
-        <v>224838.5</v>
+        <v>224963.5</v>
       </c>
       <c r="N24">
         <v>537.125</v>
@@ -5939,7 +6049,7 @@
         <v>29612.75</v>
       </c>
       <c r="M25">
-        <v>225918.75</v>
+        <v>226043.75</v>
       </c>
       <c r="N25">
         <v>546.52499999999998</v>
@@ -5992,7 +6102,7 @@
         <v>22297.75</v>
       </c>
       <c r="M26">
-        <v>223642</v>
+        <v>223767</v>
       </c>
       <c r="N26">
         <v>615.70000000000005</v>
@@ -6045,7 +6155,7 @@
         <v>23111.75</v>
       </c>
       <c r="M27">
-        <v>222562.25</v>
+        <v>222687.25</v>
       </c>
       <c r="N27">
         <v>615.29999999999995</v>
@@ -6183,16 +6293,16 @@
         <v>23.2</v>
       </c>
       <c r="F30">
-        <v>77.397913561847986</v>
+        <v>77.363095238095241</v>
       </c>
       <c r="G30">
-        <v>3.1357675111773471</v>
+        <v>3.133482142857142</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
       <c r="I30">
-        <v>203.89269746646801</v>
+        <v>204.48214285714289</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -6201,10 +6311,10 @@
         <v>116.075</v>
       </c>
       <c r="L30">
-        <v>34203</v>
+        <v>34353</v>
       </c>
       <c r="M30">
-        <v>232420.75</v>
+        <v>232570.75</v>
       </c>
       <c r="N30">
         <v>413.35</v>
@@ -6257,7 +6367,7 @@
         <v>29999.5</v>
       </c>
       <c r="M31">
-        <v>239291</v>
+        <v>239441</v>
       </c>
       <c r="N31">
         <v>618.95000000000005</v>
@@ -6310,7 +6420,7 @@
         <v>25896.75</v>
       </c>
       <c r="M32">
-        <v>234154.75</v>
+        <v>234304.75</v>
       </c>
       <c r="N32">
         <v>598.82500000000005</v>
@@ -6363,7 +6473,7 @@
         <v>31963.5</v>
       </c>
       <c r="M33">
-        <v>232150.5</v>
+        <v>232300.5</v>
       </c>
       <c r="N33">
         <v>558.45000000000005</v>
@@ -6416,7 +6526,7 @@
         <v>20294.75</v>
       </c>
       <c r="M34">
-        <v>229593.75</v>
+        <v>229743.75</v>
       </c>
       <c r="N34">
         <v>669.17499999999995</v>
@@ -6469,7 +6579,7 @@
         <v>5376</v>
       </c>
       <c r="M35">
-        <v>224954.25</v>
+        <v>225104.25</v>
       </c>
       <c r="N35">
         <v>131.19999999999999</v>
@@ -6510,7 +6620,7 @@
         <v>16</v>
       </c>
       <c r="I36">
-        <v>209.11618257261409</v>
+        <v>208.4380165289256</v>
       </c>
       <c r="J36">
         <v>8.6999999999999993</v>
@@ -6519,10 +6629,10 @@
         <v>105.72499999999999</v>
       </c>
       <c r="L36">
-        <v>25198.5</v>
+        <v>25221</v>
       </c>
       <c r="M36">
-        <v>232047.75</v>
+        <v>232220.25</v>
       </c>
       <c r="N36">
         <v>555.45000000000005</v>
@@ -6563,19 +6673,19 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>296.42907801418443</v>
+        <v>295.62897526501769</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>70.649999999999991</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="L37">
-        <v>20898.25</v>
+        <v>20915.75</v>
       </c>
       <c r="M37">
-        <v>231800.5</v>
+        <v>231990.5</v>
       </c>
       <c r="N37">
         <v>352.4</v>
@@ -6622,13 +6732,13 @@
         <v>5.05</v>
       </c>
       <c r="K38">
-        <v>67.199999999999989</v>
+        <v>67.2</v>
       </c>
       <c r="L38">
         <v>23232.75</v>
       </c>
       <c r="M38">
-        <v>238876</v>
+        <v>239066</v>
       </c>
       <c r="N38">
         <v>694.6</v>
@@ -6675,13 +6785,13 @@
         <v>15.25</v>
       </c>
       <c r="K39">
-        <v>82.449999999999989</v>
+        <v>82.45</v>
       </c>
       <c r="L39">
         <v>26927.25</v>
       </c>
       <c r="M39">
-        <v>228827.75</v>
+        <v>229017.75</v>
       </c>
       <c r="N39">
         <v>699.32500000000005</v>
@@ -6734,7 +6844,7 @@
         <v>9531.5</v>
       </c>
       <c r="M40">
-        <v>219318.75</v>
+        <v>219358.75</v>
       </c>
       <c r="N40">
         <v>305.72500000000002</v>
@@ -6787,7 +6897,7 @@
         <v>24627.75</v>
       </c>
       <c r="M41">
-        <v>213947</v>
+        <v>213987</v>
       </c>
       <c r="N41">
         <v>665.07500000000005</v>
@@ -6840,7 +6950,7 @@
         <v>21309.25</v>
       </c>
       <c r="M42">
-        <v>209359.5</v>
+        <v>209399.5</v>
       </c>
       <c r="N42">
         <v>682.85</v>
@@ -6887,13 +6997,13 @@
         <v>0.5</v>
       </c>
       <c r="K43">
-        <v>93.85</v>
+        <v>93.850000000000009</v>
       </c>
       <c r="L43">
         <v>29659.25</v>
       </c>
       <c r="M43">
-        <v>207055.25</v>
+        <v>207095.25</v>
       </c>
       <c r="N43">
         <v>640.35</v>
@@ -6940,13 +7050,13 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>92.224999999999994</v>
+        <v>92.225000000000009</v>
       </c>
       <c r="L44">
         <v>23087.75</v>
       </c>
       <c r="M44">
-        <v>207628.5</v>
+        <v>207668.5</v>
       </c>
       <c r="N44">
         <v>773.95</v>
@@ -6999,7 +7109,7 @@
         <v>23243.75</v>
       </c>
       <c r="M45">
-        <v>210802</v>
+        <v>210819.5</v>
       </c>
       <c r="N45">
         <v>841.875</v>
@@ -8686,7 +8796,7 @@
         <v>13.55</v>
       </c>
       <c r="K77">
-        <v>94.274999999999991</v>
+        <v>94.275000000000006</v>
       </c>
       <c r="L77">
         <v>24526.25</v>
@@ -8945,7 +9055,7 @@
         <v>9.9</v>
       </c>
       <c r="I82">
-        <v>174.2125748502994</v>
+        <v>174.84902840059789</v>
       </c>
       <c r="J82">
         <v>9.7749999999999986</v>
@@ -8954,10 +9064,10 @@
         <v>63.474999999999987</v>
       </c>
       <c r="L82">
-        <v>29093.5</v>
+        <v>29243.5</v>
       </c>
       <c r="M82">
-        <v>265424.75</v>
+        <v>265574.75</v>
       </c>
       <c r="N82">
         <v>900.625</v>
@@ -9010,7 +9120,7 @@
         <v>20824.5</v>
       </c>
       <c r="M83">
-        <v>258239.25</v>
+        <v>258389.25</v>
       </c>
       <c r="N83">
         <v>631.65</v>
@@ -9063,7 +9173,7 @@
         <v>27006.25</v>
       </c>
       <c r="M84">
-        <v>262936.75</v>
+        <v>263086.75</v>
       </c>
       <c r="N84">
         <v>786</v>
@@ -9116,7 +9226,7 @@
         <v>39477.75</v>
       </c>
       <c r="M85">
-        <v>276732</v>
+        <v>276882</v>
       </c>
       <c r="N85">
         <v>689.97500000000002</v>
@@ -9169,7 +9279,7 @@
         <v>24454.25</v>
       </c>
       <c r="M86">
-        <v>271848.5</v>
+        <v>271998.5</v>
       </c>
       <c r="N86">
         <v>674.02499999999998</v>
@@ -9222,7 +9332,7 @@
         <v>27241.5</v>
       </c>
       <c r="M87">
-        <v>260605.75</v>
+        <v>260755.75</v>
       </c>
       <c r="N87">
         <v>921.25</v>
@@ -9275,7 +9385,7 @@
         <v>23022.5</v>
       </c>
       <c r="M88">
-        <v>247545.75</v>
+        <v>247695.75</v>
       </c>
       <c r="N88">
         <v>890.47500000000002</v>
@@ -9328,7 +9438,7 @@
         <v>30325.25</v>
       </c>
       <c r="M89">
-        <v>243969.75</v>
+        <v>244119.75</v>
       </c>
       <c r="N89">
         <v>945.47500000000002</v>
@@ -10217,7 +10327,7 @@
         <v>0.3</v>
       </c>
       <c r="I106">
-        <v>163.2429210134128</v>
+        <v>163.89285714285711</v>
       </c>
       <c r="J106">
         <v>0.3</v>
@@ -10226,10 +10336,10 @@
         <v>132.35</v>
       </c>
       <c r="L106">
-        <v>27384</v>
+        <v>27534</v>
       </c>
       <c r="M106">
-        <v>178857</v>
+        <v>179007</v>
       </c>
       <c r="N106">
         <v>666.85</v>
@@ -10282,7 +10392,7 @@
         <v>21821.5</v>
       </c>
       <c r="M107">
-        <v>175505</v>
+        <v>175655</v>
       </c>
       <c r="N107">
         <v>579.25</v>
@@ -10335,7 +10445,7 @@
         <v>27870.75</v>
       </c>
       <c r="M108">
-        <v>185839.75</v>
+        <v>185989.75</v>
       </c>
       <c r="N108">
         <v>649.92499999999995</v>
@@ -10388,7 +10498,7 @@
         <v>28174</v>
       </c>
       <c r="M109">
-        <v>189373.75</v>
+        <v>189523.75</v>
       </c>
       <c r="N109">
         <v>822.77499999999998</v>
@@ -10441,7 +10551,7 @@
         <v>30220.75</v>
       </c>
       <c r="M110">
-        <v>205844.25</v>
+        <v>205994.25</v>
       </c>
       <c r="N110">
         <v>781.02499999999998</v>
@@ -10494,7 +10604,7 @@
         <v>30376.5</v>
       </c>
       <c r="M111">
-        <v>219091.75</v>
+        <v>219241.75</v>
       </c>
       <c r="N111">
         <v>811.9</v>
@@ -10535,19 +10645,19 @@
         <v>8.4</v>
       </c>
       <c r="I112">
-        <v>147.85373134328361</v>
+        <v>148.08047690014899</v>
       </c>
       <c r="J112">
         <v>17.45</v>
       </c>
       <c r="K112">
-        <v>45.975000000000001</v>
+        <v>45.975000000000009</v>
       </c>
       <c r="L112">
-        <v>24765.5</v>
+        <v>24840.5</v>
       </c>
       <c r="M112">
-        <v>228351.5</v>
+        <v>228576.5</v>
       </c>
       <c r="N112">
         <v>607.02499999999998</v>
@@ -10600,7 +10710,7 @@
         <v>29114</v>
       </c>
       <c r="M113">
-        <v>233790.75</v>
+        <v>234015.75</v>
       </c>
       <c r="N113">
         <v>634.9</v>
@@ -10647,13 +10757,13 @@
         <v>34.524999999999999</v>
       </c>
       <c r="K114">
-        <v>76.524999999999991</v>
+        <v>76.525000000000006</v>
       </c>
       <c r="L114">
         <v>27214</v>
       </c>
       <c r="M114">
-        <v>235176</v>
+        <v>235401</v>
       </c>
       <c r="N114">
         <v>682.875</v>
@@ -10700,13 +10810,13 @@
         <v>7.6</v>
       </c>
       <c r="K115">
-        <v>84.124999999999986</v>
+        <v>84.125</v>
       </c>
       <c r="L115">
         <v>34572.5</v>
       </c>
       <c r="M115">
-        <v>244599</v>
+        <v>244674</v>
       </c>
       <c r="N115">
         <v>792.65</v>
@@ -10747,7 +10857,7 @@
         <v>18.5</v>
       </c>
       <c r="I116">
-        <v>172.01376146788991</v>
+        <v>173.27286585365849</v>
       </c>
       <c r="J116">
         <v>39.975000000000001</v>
@@ -10756,10 +10866,10 @@
         <v>123.8</v>
       </c>
       <c r="L116">
-        <v>28124.25</v>
+        <v>28416.75</v>
       </c>
       <c r="M116">
-        <v>249275.75</v>
+        <v>249643.25</v>
       </c>
       <c r="N116">
         <v>782.875</v>
@@ -10800,7 +10910,7 @@
         <v>8.9</v>
       </c>
       <c r="I117">
-        <v>160.6214605067064</v>
+        <v>160.82886904761901</v>
       </c>
       <c r="J117">
         <v>18.074999999999999</v>
@@ -10809,10 +10919,10 @@
         <v>141.57499999999999</v>
       </c>
       <c r="L117">
-        <v>26944.25</v>
+        <v>27019.25</v>
       </c>
       <c r="M117">
-        <v>246998.25</v>
+        <v>247440.75</v>
       </c>
       <c r="N117">
         <v>812.92499999999995</v>
@@ -10865,7 +10975,7 @@
         <v>23304.25</v>
       </c>
       <c r="M118">
-        <v>242980.25</v>
+        <v>243422.75</v>
       </c>
       <c r="N118">
         <v>696</v>
@@ -10918,7 +11028,7 @@
         <v>21133</v>
       </c>
       <c r="M119">
-        <v>229848.5</v>
+        <v>230291</v>
       </c>
       <c r="N119">
         <v>691.75</v>
@@ -10971,7 +11081,7 @@
         <v>23822.75</v>
       </c>
       <c r="M120">
-        <v>226183</v>
+        <v>226625.5</v>
       </c>
       <c r="N120">
         <v>697.05</v>
@@ -11024,7 +11134,7 @@
         <v>25422.5</v>
       </c>
       <c r="M121">
-        <v>228991.25</v>
+        <v>229358.75</v>
       </c>
       <c r="N121">
         <v>560.72500000000002</v>
@@ -11077,7 +11187,7 @@
         <v>33117</v>
       </c>
       <c r="M122">
-        <v>232188</v>
+        <v>232555.5</v>
       </c>
       <c r="N122">
         <v>768.57500000000005</v>
@@ -11130,7 +11240,7 @@
         <v>29712</v>
       </c>
       <c r="M123">
-        <v>233028.5</v>
+        <v>233396</v>
       </c>
       <c r="N123">
         <v>538.92499999999995</v>
@@ -11183,7 +11293,7 @@
         <v>25439.5</v>
       </c>
       <c r="M124">
-        <v>225277</v>
+        <v>225577</v>
       </c>
       <c r="N124">
         <v>578.82500000000005</v>
@@ -11236,7 +11346,7 @@
         <v>26097</v>
       </c>
       <c r="M125">
-        <v>224863</v>
+        <v>224938</v>
       </c>
       <c r="N125">
         <v>744.80000000000007</v>
@@ -11495,7 +11605,7 @@
         <v>0</v>
       </c>
       <c r="K130">
-        <v>32.274999999999999</v>
+        <v>32.275000000000013</v>
       </c>
       <c r="L130">
         <v>26572</v>
@@ -11595,7 +11705,7 @@
         <v>39.6</v>
       </c>
       <c r="I132">
-        <v>142.6686567164179</v>
+        <v>142.4560357675112</v>
       </c>
       <c r="J132">
         <v>45.575000000000003</v>
@@ -11701,7 +11811,7 @@
         <v>0.3</v>
       </c>
       <c r="I134">
-        <v>156.61641791044781</v>
+        <v>157.14732142857139</v>
       </c>
       <c r="J134">
         <v>0.3</v>
@@ -11710,10 +11820,10 @@
         <v>99.7</v>
       </c>
       <c r="L134">
-        <v>26233.25</v>
+        <v>26400.75</v>
       </c>
       <c r="M134">
-        <v>244238.25</v>
+        <v>244405.75</v>
       </c>
       <c r="N134">
         <v>855.875</v>
@@ -11766,7 +11876,7 @@
         <v>24122</v>
       </c>
       <c r="M135">
-        <v>244811</v>
+        <v>244978.5</v>
       </c>
       <c r="N135">
         <v>642.79999999999995</v>
@@ -11819,7 +11929,7 @@
         <v>26920.25</v>
       </c>
       <c r="M136">
-        <v>234230.25</v>
+        <v>234397.75</v>
       </c>
       <c r="N136">
         <v>722.375</v>
@@ -11872,7 +11982,7 @@
         <v>21929.5</v>
       </c>
       <c r="M137">
-        <v>215063</v>
+        <v>215230.5</v>
       </c>
       <c r="N137">
         <v>656.95</v>
@@ -11925,7 +12035,7 @@
         <v>30289.75</v>
       </c>
       <c r="M138">
-        <v>219081.5</v>
+        <v>219249</v>
       </c>
       <c r="N138">
         <v>692.22500000000002</v>
@@ -11978,7 +12088,7 @@
         <v>23926.25</v>
       </c>
       <c r="M139">
-        <v>216110</v>
+        <v>216277.5</v>
       </c>
       <c r="N139">
         <v>737.67499999999995</v>
@@ -12031,7 +12141,7 @@
         <v>27068</v>
       </c>
       <c r="M140">
-        <v>219248.5</v>
+        <v>219416</v>
       </c>
       <c r="N140">
         <v>689.92499999999995</v>
@@ -12084,7 +12194,7 @@
         <v>31153</v>
       </c>
       <c r="M141">
-        <v>223721.5</v>
+        <v>223889</v>
       </c>
       <c r="N141">
         <v>812.77499999999998</v>
@@ -12116,7 +12226,7 @@
         <v>22.1</v>
       </c>
       <c r="F142">
-        <v>89.198211624441129</v>
+        <v>89.177083333333329</v>
       </c>
       <c r="G142">
         <v>1.554613095238095</v>
@@ -12125,7 +12235,7 @@
         <v>31.2</v>
       </c>
       <c r="I142">
-        <v>143.89402985074631</v>
+        <v>144.23958333333329</v>
       </c>
       <c r="J142">
         <v>105.97499999999999</v>
@@ -12134,10 +12244,10 @@
         <v>270.92500000000001</v>
       </c>
       <c r="L142">
-        <v>24102.25</v>
+        <v>24232.25</v>
       </c>
       <c r="M142">
-        <v>226525.25</v>
+        <v>226655.25</v>
       </c>
       <c r="N142">
         <v>720.47500000000002</v>
@@ -12178,7 +12288,7 @@
         <v>13.5</v>
       </c>
       <c r="I143">
-        <v>154.18250377073909</v>
+        <v>153.95030120481931</v>
       </c>
       <c r="J143">
         <v>29.074999999999999</v>
@@ -12190,7 +12300,7 @@
         <v>25555.75</v>
       </c>
       <c r="M143">
-        <v>226109</v>
+        <v>226239</v>
       </c>
       <c r="N143">
         <v>734.4</v>
@@ -12243,7 +12353,7 @@
         <v>20723.75</v>
       </c>
       <c r="M144">
-        <v>219515.25</v>
+        <v>219645.25</v>
       </c>
       <c r="N144">
         <v>606.57500000000005</v>
@@ -12296,7 +12406,7 @@
         <v>19051.25</v>
       </c>
       <c r="M145">
-        <v>214749</v>
+        <v>214879</v>
       </c>
       <c r="N145">
         <v>718.02499999999998</v>
@@ -12337,7 +12447,7 @@
         <v>7.4</v>
       </c>
       <c r="I146">
-        <v>133.60514372163391</v>
+        <v>134.00755287009059</v>
       </c>
       <c r="J146">
         <v>16.774999999999999</v>
@@ -12346,10 +12456,10 @@
         <v>266.27499999999998</v>
       </c>
       <c r="L146">
-        <v>22078.25</v>
+        <v>22178.25</v>
       </c>
       <c r="M146">
-        <v>208770.5</v>
+        <v>209000.5</v>
       </c>
       <c r="N146">
         <v>729.42499999999995</v>
@@ -12402,7 +12512,7 @@
         <v>21834.5</v>
       </c>
       <c r="M147">
-        <v>207318.5</v>
+        <v>207548.5</v>
       </c>
       <c r="N147">
         <v>716.35</v>
@@ -12455,7 +12565,7 @@
         <v>22841</v>
       </c>
       <c r="M148">
-        <v>205163.5</v>
+        <v>205393.5</v>
       </c>
       <c r="N148">
         <v>636.625</v>
@@ -12508,7 +12618,7 @@
         <v>22903</v>
       </c>
       <c r="M149">
-        <v>195518.5</v>
+        <v>195748.5</v>
       </c>
       <c r="N149">
         <v>671.15</v>
@@ -12561,7 +12671,7 @@
         <v>22888.25</v>
       </c>
       <c r="M150">
-        <v>190213.75</v>
+        <v>190338.75</v>
       </c>
       <c r="N150">
         <v>636.67499999999995</v>
@@ -12614,7 +12724,7 @@
         <v>23914.25</v>
       </c>
       <c r="M151">
-        <v>189959.25</v>
+        <v>190059.25</v>
       </c>
       <c r="N151">
         <v>644.52499999999998</v>
@@ -12667,7 +12777,7 @@
         <v>20219.25</v>
       </c>
       <c r="M152">
-        <v>188156</v>
+        <v>188256</v>
       </c>
       <c r="N152">
         <v>527.67499999999995</v>
@@ -12720,7 +12830,7 @@
         <v>22702.75</v>
       </c>
       <c r="M153">
-        <v>190086.25</v>
+        <v>190186.25</v>
       </c>
       <c r="N153">
         <v>581</v>
@@ -12796,49 +12906,155 @@
         <v>4</v>
       </c>
       <c r="C155">
-        <v>13.565625000000001</v>
+        <v>14.170833333333331</v>
       </c>
       <c r="D155">
         <v>8.6</v>
       </c>
       <c r="E155">
-        <v>20.8</v>
+        <v>21.9</v>
       </c>
       <c r="F155">
-        <v>88.052083333333329</v>
+        <v>84.78720238095238</v>
       </c>
       <c r="G155">
-        <v>2.3708333333333331</v>
+        <v>2.299404761904762</v>
       </c>
       <c r="H155">
         <v>6.1</v>
       </c>
       <c r="I155">
-        <v>119.5572916666667</v>
+        <v>146.57440476190479</v>
       </c>
       <c r="J155">
-        <v>8.7750000000000004</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="K155">
-        <v>121.175</v>
+        <v>116.72499999999999</v>
       </c>
       <c r="L155">
-        <v>5738.75</v>
+        <v>24624.5</v>
       </c>
       <c r="M155">
-        <v>192302</v>
+        <v>195892.75</v>
       </c>
       <c r="N155">
-        <v>171.15</v>
+        <v>700.7</v>
       </c>
       <c r="O155">
-        <v>4440.6500000000005</v>
+        <v>4970.2</v>
       </c>
       <c r="P155">
         <v>0</v>
       </c>
       <c r="Q155">
-        <v>2</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>45866</v>
+      </c>
+      <c r="B156">
+        <v>4</v>
+      </c>
+      <c r="C156">
+        <v>13.285565476190479</v>
+      </c>
+      <c r="D156">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="E156">
+        <v>21.1</v>
+      </c>
+      <c r="F156">
+        <v>83.523809523809518</v>
+      </c>
+      <c r="G156">
+        <v>2.5958333333333341</v>
+      </c>
+      <c r="H156">
+        <v>14.7</v>
+      </c>
+      <c r="I156">
+        <v>134.49553571428569</v>
+      </c>
+      <c r="J156">
+        <v>15.1</v>
+      </c>
+      <c r="K156">
+        <v>128.15</v>
+      </c>
+      <c r="L156">
+        <v>22595.25</v>
+      </c>
+      <c r="M156">
+        <v>195189</v>
+      </c>
+      <c r="N156">
+        <v>551.97500000000002</v>
+      </c>
+      <c r="O156">
+        <v>4885.55</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+      <c r="Q156">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>45873</v>
+      </c>
+      <c r="B157">
+        <v>4</v>
+      </c>
+      <c r="C157">
+        <v>12.93229166666667</v>
+      </c>
+      <c r="D157">
+        <v>3.6</v>
+      </c>
+      <c r="E157">
+        <v>20.6</v>
+      </c>
+      <c r="F157">
+        <v>85.626488095238102</v>
+      </c>
+      <c r="G157">
+        <v>1.9069940476190479</v>
+      </c>
+      <c r="H157">
+        <v>25.4</v>
+      </c>
+      <c r="I157">
+        <v>134.57886904761901</v>
+      </c>
+      <c r="J157">
+        <v>41.375</v>
+      </c>
+      <c r="K157">
+        <v>153.85</v>
+      </c>
+      <c r="L157">
+        <v>22609.25</v>
+      </c>
+      <c r="M157">
+        <v>195350.25</v>
+      </c>
+      <c r="N157">
+        <v>492.625</v>
+      </c>
+      <c r="O157">
+        <v>4707.0249999999996</v>
+      </c>
+      <c r="P157">
+        <v>1</v>
+      </c>
+      <c r="Q157">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12852,10 +13068,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>18</v>
       </c>
     </row>
@@ -13021,7 +13237,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -13031,16 +13247,21 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10D0B77F-24F9-40C3-B622-5B3F55C2F1AB}">
-  <dimension ref="A1:H156"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:K157"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
-    <col min="2" max="4" width="31.85546875" customWidth="1"/>
-    <col min="5" max="5" width="33.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13053,20 +13274,17 @@
       <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="K1" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>44760</v>
       </c>
@@ -13079,24 +13297,27 @@
       <c r="D2">
         <v>515.77499999999998</v>
       </c>
-      <c r="E2" cm="1">
-        <f t="array" ref="E2:E155">D2:D155*1/24</f>
-        <v>21.490624999999998</v>
-      </c>
-      <c r="F2">
-        <f>B2/296</f>
-        <v>6.1486486486486483E-2</v>
-      </c>
-      <c r="G2">
-        <f>(C2/1000)/276</f>
-        <v>7.1143115942028989E-2</v>
-      </c>
-      <c r="H2">
-        <f>F2*G2</f>
-        <v>4.3743402369761063E-3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G2" s="4">
+        <f>MAX(B2:B157)</f>
+        <v>296.27499999999998</v>
+      </c>
+      <c r="I2" cm="1">
+        <f t="array" ref="I2:I157">B2:B157/G2</f>
+        <v>6.1429415239220318E-2</v>
+      </c>
+      <c r="J2" cm="1">
+        <f t="array" ref="J2:J157">(C2:C157/1000)/G3</f>
+        <v>7.0954931124698264E-2</v>
+      </c>
+      <c r="K2">
+        <f>I2*J2</f>
+        <v>4.3587199273293674E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>44767</v>
       </c>
@@ -13109,23 +13330,25 @@
       <c r="D3">
         <v>1103.0999999999999</v>
       </c>
-      <c r="E3">
-        <v>45.962499999999999</v>
-      </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F66" si="0">B3/296</f>
-        <v>0.16655405405405405</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G66" si="1">(C3/1000)/276</f>
-        <v>0.15050543478260869</v>
-      </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H66" si="2">F3*G3</f>
-        <v>2.5067290320211513E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4">
+        <f>(MAX(C2:C157)/1000)</f>
+        <v>276.73200000000003</v>
+      </c>
+      <c r="I3">
+        <v>0.16639945996118471</v>
+      </c>
+      <c r="J3">
+        <v>0.15010732405359695</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K66" si="0">I3*J3</f>
+        <v>2.4977777658737085E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>44774</v>
       </c>
@@ -13138,23 +13361,18 @@
       <c r="D4">
         <v>1658.625</v>
       </c>
-      <c r="E4">
-        <v>69.109375</v>
-      </c>
-      <c r="F4">
+      <c r="I4">
+        <v>0.2617500632857987</v>
+      </c>
+      <c r="J4">
+        <v>0.22464604743939984</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="0"/>
-        <v>0.26199324324324325</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
-        <v>0.22524184782608697</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="2"/>
-        <v>5.9011842226057584E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>5.8801117134167441E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>44781</v>
       </c>
@@ -13167,23 +13385,18 @@
       <c r="D5">
         <v>2170.0749999999998</v>
       </c>
-      <c r="E5">
-        <v>90.419791666666654</v>
-      </c>
-      <c r="F5">
+      <c r="I5">
+        <v>0.38342755885579277</v>
+      </c>
+      <c r="J5">
+        <v>0.30838229767428416</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="0"/>
-        <v>0.38378378378378375</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>0.30920018115942033</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="2"/>
-        <v>0.11866601547199374</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.11824227159159119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>44788</v>
       </c>
@@ -13196,23 +13409,18 @@
       <c r="D6">
         <v>2703.5749999999998</v>
       </c>
-      <c r="E6">
-        <v>112.64895833333333</v>
-      </c>
-      <c r="F6">
+      <c r="I6">
+        <v>0.42865580963631766</v>
+      </c>
+      <c r="J6">
+        <v>0.41382456672882062</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="0"/>
-        <v>0.42905405405405406</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>0.41492210144927538</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="2"/>
-        <v>0.1780240097434391</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.17738830469854097</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>44795</v>
       </c>
@@ -13225,23 +13433,18 @@
       <c r="D7">
         <v>3161.7249999999999</v>
       </c>
-      <c r="E7">
-        <v>131.73854166666666</v>
-      </c>
-      <c r="F7">
+      <c r="I7">
+        <v>0.47211205805417267</v>
+      </c>
+      <c r="J7">
+        <v>0.49983287079195748</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="0"/>
-        <v>0.47255067567567566</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="1"/>
-        <v>0.50115851449275362</v>
-      </c>
-      <c r="H7">
-        <f t="shared" si="2"/>
-        <v>0.23682279464416861</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.23597712531271642</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>44802</v>
       </c>
@@ -13254,23 +13457,18 @@
       <c r="D8">
         <v>3700.75</v>
       </c>
-      <c r="E8">
-        <v>154.19791666666666</v>
-      </c>
-      <c r="F8">
+      <c r="I8">
+        <v>0.53624166736984225</v>
+      </c>
+      <c r="J8">
+        <v>0.57715406964138583</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="0"/>
-        <v>0.53673986486486491</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="1"/>
-        <v>0.57868478260869571</v>
-      </c>
-      <c r="H8">
-        <f t="shared" si="2"/>
-        <v>0.31060319201674508</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.30949406063378676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>44809</v>
       </c>
@@ -13283,23 +13481,18 @@
       <c r="D9">
         <v>4223.8</v>
       </c>
-      <c r="E9">
-        <v>175.99166666666667</v>
-      </c>
-      <c r="F9">
+      <c r="I9">
+        <v>0.53624166736984225</v>
+      </c>
+      <c r="J9">
+        <v>0.66166272783776359</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="0"/>
-        <v>0.53673986486486491</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="1"/>
-        <v>0.66341757246376809</v>
-      </c>
-      <c r="H9">
-        <f t="shared" si="2"/>
-        <v>0.35608265819317964</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.35481112441220047</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>44816</v>
       </c>
@@ -13312,23 +13505,18 @@
       <c r="D10">
         <v>4223.5249999999996</v>
       </c>
-      <c r="E10">
-        <v>175.98020833333331</v>
-      </c>
-      <c r="F10">
+      <c r="I10">
+        <v>0.58982364357438199</v>
+      </c>
+      <c r="J10">
+        <v>0.71796449272220053</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="0"/>
-        <v>0.5903716216216216</v>
-      </c>
-      <c r="G10">
-        <f t="shared" si="1"/>
-        <v>0.71986865942028988</v>
-      </c>
-      <c r="H10">
-        <f t="shared" si="2"/>
-        <v>0.42499002781653938</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.42347243305444116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>44823</v>
       </c>
@@ -13341,23 +13529,18 @@
       <c r="D11">
         <v>4097.8999999999996</v>
       </c>
-      <c r="E11">
-        <v>170.74583333333331</v>
-      </c>
-      <c r="F11">
+      <c r="I11">
+        <v>0.66391021854695809</v>
+      </c>
+      <c r="J11">
+        <v>0.73492584883569656</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="0"/>
-        <v>0.66452702702702704</v>
-      </c>
-      <c r="G11">
-        <f t="shared" si="1"/>
-        <v>0.73687499999999995</v>
-      </c>
-      <c r="H11">
-        <f t="shared" si="2"/>
-        <v>0.48967335304054049</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.48792478091631597</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>44830</v>
       </c>
@@ -13370,23 +13553,18 @@
       <c r="D12">
         <v>4107.6499999999996</v>
       </c>
-      <c r="E12">
-        <v>171.15208333333331</v>
-      </c>
-      <c r="F12">
+      <c r="I12">
+        <v>0.63834275588557932</v>
+      </c>
+      <c r="J12">
+        <v>0.75274272581414503</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="0"/>
-        <v>0.63893581081081086</v>
-      </c>
-      <c r="G12">
-        <f t="shared" si="1"/>
-        <v>0.75473913043478258</v>
-      </c>
-      <c r="H12">
-        <f t="shared" si="2"/>
-        <v>0.48222985825499415</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.48050786606902435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>44837</v>
       </c>
@@ -13399,23 +13577,18 @@
       <c r="D13">
         <v>4142.5</v>
       </c>
-      <c r="E13">
-        <v>172.60416666666666</v>
-      </c>
-      <c r="F13">
+      <c r="I13">
+        <v>0.68095519365454393</v>
+      </c>
+      <c r="J13">
+        <v>0.7557926080106383</v>
+      </c>
+      <c r="K13">
         <f t="shared" si="0"/>
-        <v>0.68158783783783783</v>
-      </c>
-      <c r="G13">
-        <f t="shared" si="1"/>
-        <v>0.75779710144927537</v>
-      </c>
-      <c r="H13">
-        <f t="shared" si="2"/>
-        <v>0.51650528789659222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.51466090175055701</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>44844</v>
       </c>
@@ -13428,23 +13601,18 @@
       <c r="D14">
         <v>3689.3</v>
       </c>
-      <c r="E14">
-        <v>153.72083333333333</v>
-      </c>
-      <c r="F14">
+      <c r="I14">
+        <v>0.68095519365454393</v>
+      </c>
+      <c r="J14">
+        <v>0.75640963097870861</v>
+      </c>
+      <c r="K14">
         <f t="shared" si="0"/>
-        <v>0.68158783783783783</v>
-      </c>
-      <c r="G14">
-        <f t="shared" si="1"/>
-        <v>0.7584157608695653</v>
-      </c>
-      <c r="H14">
-        <f t="shared" si="2"/>
-        <v>0.51692695863322569</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.51508106674526866</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>44851</v>
       </c>
@@ -13457,23 +13625,18 @@
       <c r="D15">
         <v>3561.9250000000002</v>
       </c>
-      <c r="E15">
-        <v>148.41354166666667</v>
-      </c>
-      <c r="F15">
+      <c r="I15">
+        <v>0.61547548730064972</v>
+      </c>
+      <c r="J15">
+        <v>0.74905413902259221</v>
+      </c>
+      <c r="K15">
         <f t="shared" si="0"/>
-        <v>0.61604729729729724</v>
-      </c>
-      <c r="G15">
-        <f t="shared" si="1"/>
-        <v>0.75104076086956517</v>
-      </c>
-      <c r="H15">
-        <f t="shared" si="2"/>
-        <v>0.46267663089380134</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.46102446122949858</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>44858</v>
       </c>
@@ -13486,23 +13649,18 @@
       <c r="D16">
         <v>3537.4749999999999</v>
       </c>
-      <c r="E16">
-        <v>147.39479166666666</v>
-      </c>
-      <c r="F16">
+      <c r="I16">
+        <v>0.65699097122605699</v>
+      </c>
+      <c r="J16">
+        <v>0.72191325903762482</v>
+      </c>
+      <c r="K16">
         <f t="shared" si="0"/>
-        <v>0.65760135135135134</v>
-      </c>
-      <c r="G16">
-        <f t="shared" si="1"/>
-        <v>0.7238278985507246</v>
-      </c>
-      <c r="H16">
-        <f t="shared" si="2"/>
-        <v>0.47599020423276533</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.47429049319609717</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>44865</v>
       </c>
@@ -13515,23 +13673,18 @@
       <c r="D17">
         <v>3576.125</v>
       </c>
-      <c r="E17">
-        <v>149.00520833333334</v>
-      </c>
-      <c r="F17">
+      <c r="I17">
+        <v>0.65505020673360903</v>
+      </c>
+      <c r="J17">
+        <v>0.72666063194715458</v>
+      </c>
+      <c r="K17">
         <f t="shared" si="0"/>
-        <v>0.65565878378378373</v>
-      </c>
-      <c r="G17">
-        <f t="shared" si="1"/>
-        <v>0.72858786231884054</v>
-      </c>
-      <c r="H17">
-        <f t="shared" si="2"/>
-        <v>0.47770503168759787</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.47599919718215861</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>44872</v>
       </c>
@@ -13544,23 +13697,18 @@
       <c r="D18">
         <v>3680.0250000000001</v>
       </c>
-      <c r="E18">
-        <v>153.33437499999999</v>
-      </c>
-      <c r="F18">
+      <c r="I18">
+        <v>0.67884566703231797</v>
+      </c>
+      <c r="J18">
+        <v>0.73457261899599613</v>
+      </c>
+      <c r="K18">
         <f t="shared" si="0"/>
-        <v>0.67947635135135132</v>
-      </c>
-      <c r="G18">
-        <f t="shared" si="1"/>
-        <v>0.7365208333333334</v>
-      </c>
-      <c r="H18">
-        <f t="shared" si="2"/>
-        <v>0.50044848852759016</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.49866143952601377</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>44879</v>
       </c>
@@ -13573,23 +13721,18 @@
       <c r="D19">
         <v>3905.7750000000001</v>
       </c>
-      <c r="E19">
-        <v>162.74062499999999</v>
-      </c>
-      <c r="F19">
+      <c r="I19">
+        <v>0.77301493544848543</v>
+      </c>
+      <c r="J19">
+        <v>0.73371167772429635</v>
+      </c>
+      <c r="K19">
         <f t="shared" si="0"/>
-        <v>0.77373310810810814</v>
-      </c>
-      <c r="G19">
-        <f t="shared" si="1"/>
-        <v>0.73565760869565222</v>
-      </c>
-      <c r="H19">
-        <f t="shared" si="2"/>
-        <v>0.56920264807946541</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.56717008519384693</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>44886</v>
       </c>
@@ -13602,23 +13745,18 @@
       <c r="D20">
         <v>3946.0749999999998</v>
       </c>
-      <c r="E20">
-        <v>164.41979166666667</v>
-      </c>
-      <c r="F20">
+      <c r="I20">
+        <v>0.68508986583410691</v>
+      </c>
+      <c r="J20">
+        <v>0.74373220299784626</v>
+      </c>
+      <c r="K20">
         <f t="shared" si="0"/>
-        <v>0.68572635135135129</v>
-      </c>
-      <c r="G20">
-        <f t="shared" si="1"/>
-        <v>0.74570471014492756</v>
-      </c>
-      <c r="H20">
-        <f t="shared" si="2"/>
-        <v>0.51134937007319814</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.50952339516829925</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>44893</v>
       </c>
@@ -13631,23 +13769,18 @@
       <c r="D21">
         <v>3949.75</v>
       </c>
-      <c r="E21">
-        <v>164.57291666666666</v>
-      </c>
-      <c r="F21">
+      <c r="I21">
+        <v>0.61986330267487988</v>
+      </c>
+      <c r="J21">
+        <v>0.75265148230056511</v>
+      </c>
+      <c r="K21">
         <f t="shared" si="0"/>
-        <v>0.62043918918918917</v>
-      </c>
-      <c r="G21">
-        <f t="shared" si="1"/>
-        <v>0.75464764492753622</v>
-      </c>
-      <c r="H21">
-        <f t="shared" si="2"/>
-        <v>0.46821297294237169</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.46654103358197219</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>44900</v>
       </c>
@@ -13660,23 +13793,18 @@
       <c r="D22">
         <v>4393.2250000000004</v>
       </c>
-      <c r="E22">
-        <v>183.05104166666669</v>
-      </c>
-      <c r="F22">
+      <c r="I22">
+        <v>0.5567462661378787</v>
+      </c>
+      <c r="J22">
+        <v>0.73542904326207303</v>
+      </c>
+      <c r="K22">
         <f t="shared" si="0"/>
-        <v>0.55726351351351344</v>
-      </c>
-      <c r="G22">
-        <f t="shared" si="1"/>
-        <v>0.73737952898550729</v>
-      </c>
-      <c r="H22">
-        <f t="shared" si="2"/>
-        <v>0.4109147071154034</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.40944737384551161</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>44907</v>
       </c>
@@ -13689,23 +13817,18 @@
       <c r="D23">
         <v>4453.9250000000002</v>
       </c>
-      <c r="E23">
-        <v>185.58020833333333</v>
-      </c>
-      <c r="F23">
+      <c r="I23">
+        <v>0.51430259049869209</v>
+      </c>
+      <c r="J23">
+        <v>0.74312963444776892</v>
+      </c>
+      <c r="K23">
         <f t="shared" si="0"/>
-        <v>0.51478040540540537</v>
-      </c>
-      <c r="G23">
-        <f t="shared" si="1"/>
-        <v>0.74510054347826082</v>
-      </c>
-      <c r="H23">
-        <f t="shared" si="2"/>
-        <v>0.38356315983952699</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.38219349607283365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>44914</v>
       </c>
@@ -13718,23 +13841,18 @@
       <c r="D24">
         <v>4476.4750000000004</v>
       </c>
-      <c r="E24">
-        <v>186.51979166666669</v>
-      </c>
-      <c r="F24">
+      <c r="I24">
+        <v>0.43464686524343943</v>
+      </c>
+      <c r="J24">
+        <v>0.81247741497188608</v>
+      </c>
+      <c r="K24">
         <f t="shared" si="0"/>
-        <v>0.43505067567567568</v>
-      </c>
-      <c r="G24">
-        <f t="shared" si="1"/>
-        <v>0.81463224637681164</v>
-      </c>
-      <c r="H24">
-        <f t="shared" si="2"/>
-        <v>0.35440630921342542</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.35314076149862339</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>44921</v>
       </c>
@@ -13747,23 +13865,18 @@
       <c r="D25">
         <v>4461.3</v>
       </c>
-      <c r="E25">
-        <v>185.88750000000002</v>
-      </c>
-      <c r="F25">
+      <c r="I25">
+        <v>0.36731077546198637</v>
+      </c>
+      <c r="J25">
+        <v>0.81638101123108264</v>
+      </c>
+      <c r="K25">
         <f t="shared" si="0"/>
-        <v>0.36765202702702704</v>
-      </c>
-      <c r="G25">
-        <f t="shared" si="1"/>
-        <v>0.8185461956521739</v>
-      </c>
-      <c r="H25">
-        <f t="shared" si="2"/>
-        <v>0.3009401680467832</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.29986554230772955</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>44928</v>
       </c>
@@ -13776,23 +13889,18 @@
       <c r="D26">
         <v>4457.6000000000004</v>
       </c>
-      <c r="E26">
-        <v>185.73333333333335</v>
-      </c>
-      <c r="F26">
+      <c r="I26">
+        <v>0.32166061935701629</v>
+      </c>
+      <c r="J26">
+        <v>0.8081537371897719</v>
+      </c>
+      <c r="K26">
         <f t="shared" si="0"/>
-        <v>0.32195945945945947</v>
-      </c>
-      <c r="G26">
-        <f t="shared" si="1"/>
-        <v>0.81029710144927536</v>
-      </c>
-      <c r="H26">
-        <f t="shared" si="2"/>
-        <v>0.26088281678417546</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.25995123164014938</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>44935</v>
       </c>
@@ -13805,23 +13913,18 @@
       <c r="D27">
         <v>4385.45</v>
       </c>
-      <c r="E27">
-        <v>182.72708333333333</v>
-      </c>
-      <c r="F27">
+      <c r="I27">
+        <v>0.46038309003459627</v>
+      </c>
+      <c r="J27">
+        <v>0.80425194773282449</v>
+      </c>
+      <c r="K27">
         <f t="shared" si="0"/>
-        <v>0.46081081081081082</v>
-      </c>
-      <c r="G27">
-        <f t="shared" si="1"/>
-        <v>0.80638496376811597</v>
-      </c>
-      <c r="H27">
-        <f t="shared" si="2"/>
-        <v>0.37159090897963182</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.37026399686358036</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>44942</v>
       </c>
@@ -13834,23 +13937,18 @@
       <c r="D28">
         <v>4126.6750000000002</v>
       </c>
-      <c r="E28">
-        <v>171.94479166666667</v>
-      </c>
-      <c r="F28">
+      <c r="I28">
+        <v>0.49751075858577343</v>
+      </c>
+      <c r="J28">
+        <v>0.77953850656953294</v>
+      </c>
+      <c r="K28">
         <f t="shared" si="0"/>
-        <v>0.49797297297297299</v>
-      </c>
-      <c r="G28">
-        <f t="shared" si="1"/>
-        <v>0.78160597826086964</v>
-      </c>
-      <c r="H28">
-        <f t="shared" si="2"/>
-        <v>0.38921865268801414</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.38782879375022927</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>44949</v>
       </c>
@@ -13863,23 +13961,18 @@
       <c r="D29">
         <v>3925.25</v>
       </c>
-      <c r="E29">
-        <v>163.55208333333334</v>
-      </c>
-      <c r="F29">
+      <c r="I29">
+        <v>0.43084971732343269</v>
+      </c>
+      <c r="J29">
+        <v>0.80578140583669389</v>
+      </c>
+      <c r="K29">
         <f t="shared" si="0"/>
-        <v>0.43125000000000002</v>
-      </c>
-      <c r="G29">
-        <f t="shared" si="1"/>
-        <v>0.8079184782608696</v>
-      </c>
-      <c r="H29">
-        <f t="shared" si="2"/>
-        <v>0.34841484375000004</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.34717069092921776</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>44956</v>
       </c>
@@ -13892,23 +13985,18 @@
       <c r="D30">
         <v>3814.8249999999998</v>
       </c>
-      <c r="E30">
-        <v>158.95104166666667</v>
-      </c>
-      <c r="F30">
+      <c r="I30">
+        <v>0.39178128427980763</v>
+      </c>
+      <c r="J30">
+        <v>0.8398766676784758</v>
+      </c>
+      <c r="K30">
         <f t="shared" si="0"/>
-        <v>0.3921452702702703</v>
-      </c>
-      <c r="G30">
-        <f t="shared" si="1"/>
-        <v>0.84210416666666665</v>
-      </c>
-      <c r="H30">
-        <f t="shared" si="2"/>
-        <v>0.33022716603322072</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.32904795949971843</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>44963</v>
       </c>
@@ -13921,23 +14009,18 @@
       <c r="D31">
         <v>4042.3</v>
       </c>
-      <c r="E31">
-        <v>168.42916666666667</v>
-      </c>
-      <c r="F31">
+      <c r="I31">
+        <v>0.40688549489494558</v>
+      </c>
+      <c r="J31">
+        <v>0.86470303398233661</v>
+      </c>
+      <c r="K31">
         <f t="shared" si="0"/>
-        <v>0.40726351351351353</v>
-      </c>
-      <c r="G31">
-        <f t="shared" si="1"/>
-        <v>0.86699637681159414</v>
-      </c>
-      <c r="H31">
-        <f t="shared" si="2"/>
-        <v>0.35309599062377595</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.35183512191906396</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>44970</v>
       </c>
@@ -13950,23 +14033,18 @@
       <c r="D32">
         <v>4104</v>
       </c>
-      <c r="E32">
-        <v>171</v>
-      </c>
-      <c r="F32">
+      <c r="I32">
+        <v>0.45405451016791837</v>
+      </c>
+      <c r="J32">
+        <v>0.8461426578783805</v>
+      </c>
+      <c r="K32">
         <f t="shared" si="0"/>
-        <v>0.45447635135135139</v>
-      </c>
-      <c r="G32">
-        <f t="shared" si="1"/>
-        <v>0.84838677536231888</v>
-      </c>
-      <c r="H32">
-        <f t="shared" si="2"/>
-        <v>0.38557172620140528</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.38419489005514862</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>44977</v>
       </c>
@@ -13979,23 +14057,18 @@
       <c r="D33">
         <v>4115.9250000000002</v>
       </c>
-      <c r="E33">
-        <v>171.49687500000002</v>
-      </c>
-      <c r="F33">
+      <c r="I33">
+        <v>0.51565268753691673</v>
+      </c>
+      <c r="J33">
+        <v>0.83890009106283325</v>
+      </c>
+      <c r="K33">
         <f t="shared" si="0"/>
-        <v>0.51613175675675682</v>
-      </c>
-      <c r="G33">
-        <f t="shared" si="1"/>
-        <v>0.84112500000000001</v>
-      </c>
-      <c r="H33">
-        <f t="shared" si="2"/>
-        <v>0.43413132390202708</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.43258108653151417</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>44984</v>
       </c>
@@ -14008,23 +14081,18 @@
       <c r="D34">
         <v>4169.3999999999996</v>
       </c>
-      <c r="E34">
-        <v>173.72499999999999</v>
-      </c>
-      <c r="F34">
+      <c r="I34">
+        <v>0.50864905915112646</v>
+      </c>
+      <c r="J34">
+        <v>0.82966100776202234</v>
+      </c>
+      <c r="K34">
         <f t="shared" si="0"/>
-        <v>0.50912162162162156</v>
-      </c>
-      <c r="G34">
-        <f t="shared" si="1"/>
-        <v>0.83186141304347827</v>
-      </c>
-      <c r="H34">
-        <f t="shared" si="2"/>
-        <v>0.42351863157314917</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.42200629101252807</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>44991</v>
       </c>
@@ -14037,23 +14105,18 @@
       <c r="D35">
         <v>3685.3</v>
       </c>
-      <c r="E35">
-        <v>153.55416666666667</v>
-      </c>
-      <c r="F35">
+      <c r="I35">
+        <v>0.51210868281157707</v>
+      </c>
+      <c r="J35">
+        <v>0.81289568969255444</v>
+      </c>
+      <c r="K35">
         <f t="shared" si="0"/>
-        <v>0.51258445945945941</v>
-      </c>
-      <c r="G35">
-        <f t="shared" si="1"/>
-        <v>0.81505163043478257</v>
-      </c>
-      <c r="H35">
-        <f t="shared" si="2"/>
-        <v>0.41778279941796409</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.41629094091166252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>44998</v>
       </c>
@@ -14066,28 +14129,23 @@
       <c r="D36">
         <v>3893.95</v>
       </c>
-      <c r="E36">
-        <v>162.24791666666667</v>
-      </c>
-      <c r="F36">
+      <c r="I36">
+        <v>0.35684752341574549</v>
+      </c>
+      <c r="J36">
+        <v>0.83852879320064178</v>
+      </c>
+      <c r="K36">
         <f t="shared" si="0"/>
-        <v>0.35717905405405403</v>
-      </c>
-      <c r="G36">
-        <f t="shared" si="1"/>
-        <v>0.84075271739130442</v>
-      </c>
-      <c r="H36">
-        <f t="shared" si="2"/>
-        <v>0.30029926029120152</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.29922692316644284</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>45005</v>
       </c>
       <c r="B37">
-        <v>70.649999999999991</v>
+        <v>70.650000000000006</v>
       </c>
       <c r="C37">
         <v>231800.5</v>
@@ -14095,28 +14153,23 @@
       <c r="D37">
         <v>3897.8</v>
       </c>
-      <c r="E37">
-        <v>162.40833333333333</v>
-      </c>
-      <c r="F37">
+      <c r="I37">
+        <v>0.23846088937642396</v>
+      </c>
+      <c r="J37">
+        <v>0.83763532948845809</v>
+      </c>
+      <c r="K37">
         <f t="shared" si="0"/>
-        <v>0.2386824324324324</v>
-      </c>
-      <c r="G37">
-        <f t="shared" si="1"/>
-        <v>0.83985688405797099</v>
-      </c>
-      <c r="H37">
-        <f t="shared" si="2"/>
-        <v>0.20045908398207987</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.19974326564293163</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>45012</v>
       </c>
       <c r="B38">
-        <v>67.199999999999989</v>
+        <v>67.2</v>
       </c>
       <c r="C38">
         <v>238876</v>
@@ -14124,28 +14177,23 @@
       <c r="D38">
         <v>4179.05</v>
       </c>
-      <c r="E38">
-        <v>174.12708333333333</v>
-      </c>
-      <c r="F38">
+      <c r="I38">
+        <v>0.22681630242173659</v>
+      </c>
+      <c r="J38">
+        <v>0.86320338811557751</v>
+      </c>
+      <c r="K38">
         <f t="shared" si="0"/>
-        <v>0.22702702702702698</v>
-      </c>
-      <c r="G38">
-        <f t="shared" si="1"/>
-        <v>0.86549275362318845</v>
-      </c>
-      <c r="H38">
-        <f t="shared" si="2"/>
-        <v>0.1964902467685076</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.1957886007302905</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>45019</v>
       </c>
       <c r="B39">
-        <v>82.449999999999989</v>
+        <v>82.45</v>
       </c>
       <c r="C39">
         <v>228827.75</v>
@@ -14153,23 +14201,18 @@
       <c r="D39">
         <v>4259.4250000000002</v>
       </c>
-      <c r="E39">
-        <v>177.47604166666667</v>
-      </c>
-      <c r="F39">
+      <c r="I39">
+        <v>0.27828875200405034</v>
+      </c>
+      <c r="J39">
+        <v>0.82689298671638978</v>
+      </c>
+      <c r="K39">
         <f t="shared" si="0"/>
-        <v>0.27854729729729727</v>
-      </c>
-      <c r="G39">
-        <f t="shared" si="1"/>
-        <v>0.8290860507246377</v>
-      </c>
-      <c r="H39">
-        <f t="shared" si="2"/>
-        <v>0.23093967865623774</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.23011501731420589</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>45026</v>
       </c>
@@ -14182,23 +14225,18 @@
       <c r="D40">
         <v>3966.3249999999998</v>
       </c>
-      <c r="E40">
-        <v>165.26354166666667</v>
-      </c>
-      <c r="F40">
+      <c r="I40">
+        <v>0.28107332714538857</v>
+      </c>
+      <c r="J40">
+        <v>0.79253122154286448</v>
+      </c>
+      <c r="K40">
         <f t="shared" si="0"/>
-        <v>0.28133445945945945</v>
-      </c>
-      <c r="G40">
-        <f t="shared" si="1"/>
-        <v>0.79463315217391306</v>
-      </c>
-      <c r="H40">
-        <f t="shared" si="2"/>
-        <v>0.22355768833541423</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.22275938730565198</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>45033</v>
       </c>
@@ -14211,23 +14249,18 @@
       <c r="D41">
         <v>4072.95</v>
       </c>
-      <c r="E41">
-        <v>169.70624999999998</v>
-      </c>
-      <c r="F41">
+      <c r="I41">
+        <v>0.40469158720783061</v>
+      </c>
+      <c r="J41">
+        <v>0.77311984157957869</v>
+      </c>
+      <c r="K41">
         <f t="shared" si="0"/>
-        <v>0.40506756756756757</v>
-      </c>
-      <c r="G41">
-        <f t="shared" si="1"/>
-        <v>0.77517028985507253</v>
-      </c>
-      <c r="H41">
-        <f t="shared" si="2"/>
-        <v>0.3139963437622405</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.31287509579070627</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>45040</v>
       </c>
@@ -14240,23 +14273,18 @@
       <c r="D42">
         <v>4086.625</v>
       </c>
-      <c r="E42">
-        <v>170.27604166666666</v>
-      </c>
-      <c r="F42">
+      <c r="I42">
+        <v>0.37768964644333819</v>
+      </c>
+      <c r="J42">
+        <v>0.75654243094401796</v>
+      </c>
+      <c r="K42">
         <f t="shared" si="0"/>
-        <v>0.37804054054054054</v>
-      </c>
-      <c r="G42">
-        <f t="shared" si="1"/>
-        <v>0.75854891304347827</v>
-      </c>
-      <c r="H42">
-        <f t="shared" si="2"/>
-        <v>0.28676224111339599</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.28573824326262975</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>45047</v>
       </c>
@@ -14269,23 +14297,18 @@
       <c r="D43">
         <v>4595.7750000000005</v>
       </c>
-      <c r="E43">
-        <v>191.49062500000002</v>
-      </c>
-      <c r="F43">
+      <c r="I43">
+        <v>0.31676651759345203</v>
+      </c>
+      <c r="J43">
+        <v>0.74821578277900636</v>
+      </c>
+      <c r="K43">
         <f t="shared" si="0"/>
-        <v>0.31706081081081078</v>
-      </c>
-      <c r="G43">
-        <f t="shared" si="1"/>
-        <v>0.75020018115942033</v>
-      </c>
-      <c r="H43">
-        <f t="shared" si="2"/>
-        <v>0.23785907770882295</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.2370097079193646</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>45054</v>
       </c>
@@ -14298,23 +14321,18 @@
       <c r="D44">
         <v>4814.2750000000005</v>
       </c>
-      <c r="E44">
-        <v>200.59479166666668</v>
-      </c>
-      <c r="F44">
+      <c r="I44">
+        <v>0.31128174837566452</v>
+      </c>
+      <c r="J44">
+        <v>0.75028728155760804</v>
+      </c>
+      <c r="K44">
         <f t="shared" si="0"/>
-        <v>0.31157094594594592</v>
-      </c>
-      <c r="G44">
-        <f t="shared" si="1"/>
-        <v>0.7522771739130435</v>
-      </c>
-      <c r="H44">
-        <f t="shared" si="2"/>
-        <v>0.23438771068962982</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.2335507367872767</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>45061</v>
       </c>
@@ -14327,23 +14345,18 @@
       <c r="D45">
         <v>5303.75</v>
       </c>
-      <c r="E45">
-        <v>220.98958333333334</v>
-      </c>
-      <c r="F45">
+      <c r="I45">
+        <v>0.2734790313053751</v>
+      </c>
+      <c r="J45">
+        <v>0.76175505543269295</v>
+      </c>
+      <c r="K45">
         <f t="shared" si="0"/>
-        <v>0.27373310810810814</v>
-      </c>
-      <c r="G45">
-        <f t="shared" si="1"/>
-        <v>0.76377536231884058</v>
-      </c>
-      <c r="H45">
-        <f t="shared" si="2"/>
-        <v>0.20907060382393264</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.20832403465170518</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45068</v>
       </c>
@@ -14356,23 +14369,18 @@
       <c r="D46">
         <v>5343.625</v>
       </c>
-      <c r="E46">
-        <v>222.65104166666666</v>
-      </c>
-      <c r="F46">
+      <c r="I46">
+        <v>0.3919500464095857</v>
+      </c>
+      <c r="J46">
+        <v>0.72268024659237096</v>
+      </c>
+      <c r="K46">
         <f t="shared" si="0"/>
-        <v>0.3923141891891892</v>
-      </c>
-      <c r="G46">
-        <f t="shared" si="1"/>
-        <v>0.72459692028985512</v>
-      </c>
-      <c r="H46">
-        <f t="shared" si="2"/>
-        <v>0.28426965327249809</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.28325455619117063</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>45075</v>
       </c>
@@ -14385,23 +14393,18 @@
       <c r="D47">
         <v>5361.5999999999995</v>
       </c>
-      <c r="E47">
-        <v>223.39999999999998</v>
-      </c>
-      <c r="F47">
+      <c r="I47">
+        <v>0.41262340730740027</v>
+      </c>
+      <c r="J47">
+        <v>0.72145884827197426</v>
+      </c>
+      <c r="K47">
         <f t="shared" si="0"/>
-        <v>0.41300675675675674</v>
-      </c>
-      <c r="G47">
-        <f t="shared" si="1"/>
-        <v>0.72337228260869557</v>
-      </c>
-      <c r="H47">
-        <f t="shared" si="2"/>
-        <v>0.29875764036794944</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.2976908082060547</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>45082</v>
       </c>
@@ -14414,23 +14417,18 @@
       <c r="D48">
         <v>5735.3250000000007</v>
       </c>
-      <c r="E48">
-        <v>238.97187500000004</v>
-      </c>
-      <c r="F48">
+      <c r="I48">
+        <v>0.43405619778921611</v>
+      </c>
+      <c r="J48">
+        <v>0.71492816154257544</v>
+      </c>
+      <c r="K48">
         <f t="shared" si="0"/>
-        <v>0.43445945945945946</v>
-      </c>
-      <c r="G48">
-        <f t="shared" si="1"/>
-        <v>0.71682427536231885</v>
-      </c>
-      <c r="H48">
-        <f t="shared" si="2"/>
-        <v>0.31143108720133178</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.3103189994916048</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>45089</v>
       </c>
@@ -14443,23 +14441,18 @@
       <c r="D49">
         <v>5687.5</v>
       </c>
-      <c r="E49">
-        <v>236.97916666666666</v>
-      </c>
-      <c r="F49">
+      <c r="I49">
+        <v>0.41802379546029872</v>
+      </c>
+      <c r="J49">
+        <v>0.71089628232369206</v>
+      </c>
+      <c r="K49">
         <f t="shared" si="0"/>
-        <v>0.41841216216216215</v>
-      </c>
-      <c r="G49">
-        <f t="shared" si="1"/>
-        <v>0.7127817028985507</v>
-      </c>
-      <c r="H49">
-        <f t="shared" si="2"/>
-        <v>0.29823653345941048</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.29717156211556583</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>45096</v>
       </c>
@@ -14472,23 +14465,18 @@
       <c r="D50">
         <v>5814.6750000000002</v>
       </c>
-      <c r="E50">
-        <v>242.27812500000002</v>
-      </c>
-      <c r="F50">
+      <c r="I50">
+        <v>0.34435912581216782</v>
+      </c>
+      <c r="J50">
+        <v>0.72350143821459023</v>
+      </c>
+      <c r="K50">
         <f t="shared" si="0"/>
-        <v>0.34467905405405408</v>
-      </c>
-      <c r="G50">
-        <f t="shared" si="1"/>
-        <v>0.72542028985507245</v>
-      </c>
-      <c r="H50">
-        <f t="shared" si="2"/>
-        <v>0.2500371792988641</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.24914432278742243</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>45103</v>
       </c>
@@ -14501,23 +14489,18 @@
       <c r="D51">
         <v>5940.5249999999996</v>
       </c>
-      <c r="E51">
-        <v>247.52187499999999</v>
-      </c>
-      <c r="F51">
+      <c r="I51">
+        <v>0.34106826428149523</v>
+      </c>
+      <c r="J51">
+        <v>0.72044523221022494</v>
+      </c>
+      <c r="K51">
         <f t="shared" si="0"/>
-        <v>0.34138513513513513</v>
-      </c>
-      <c r="G51">
-        <f t="shared" si="1"/>
-        <v>0.72235597826086961</v>
-      </c>
-      <c r="H51">
-        <f t="shared" si="2"/>
-        <v>0.2466015932542597</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.24572100485982021</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>45110</v>
       </c>
@@ -14530,23 +14513,18 @@
       <c r="D52">
         <v>5778.5249999999996</v>
       </c>
-      <c r="E52">
-        <v>240.77187499999999</v>
-      </c>
-      <c r="F52">
+      <c r="I52">
+        <v>0.44553202261412544</v>
+      </c>
+      <c r="J52">
+        <v>0.69773643814231823</v>
+      </c>
+      <c r="K52">
         <f t="shared" si="0"/>
-        <v>0.44594594594594594</v>
-      </c>
-      <c r="G52">
-        <f t="shared" si="1"/>
-        <v>0.69958695652173919</v>
-      </c>
-      <c r="H52">
-        <f t="shared" si="2"/>
-        <v>0.31197796709753234</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.31086392653712264</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>45117</v>
       </c>
@@ -14559,23 +14537,18 @@
       <c r="D53">
         <v>5594.15</v>
       </c>
-      <c r="E53">
-        <v>233.08958333333331</v>
-      </c>
-      <c r="F53">
+      <c r="I53">
+        <v>0.47835625685596156</v>
+      </c>
+      <c r="J53">
+        <v>0.69141714727606485</v>
+      </c>
+      <c r="K53">
         <f t="shared" si="0"/>
-        <v>0.47880067567567564</v>
-      </c>
-      <c r="G53">
-        <f t="shared" si="1"/>
-        <v>0.69325090579710147</v>
-      </c>
-      <c r="H53">
-        <f t="shared" si="2"/>
-        <v>0.33192900210842635</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.33074371849700546</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>45124</v>
       </c>
@@ -14588,23 +14561,18 @@
       <c r="D54">
         <v>5525.9</v>
       </c>
-      <c r="E54">
-        <v>230.24583333333331</v>
-      </c>
-      <c r="F54">
+      <c r="I54">
+        <v>0.45143869715635815</v>
+      </c>
+      <c r="J54">
+        <v>0.68775475911712403</v>
+      </c>
+      <c r="K54">
         <f t="shared" si="0"/>
-        <v>0.45185810810810811</v>
-      </c>
-      <c r="G54">
-        <f t="shared" si="1"/>
-        <v>0.68957880434782604</v>
-      </c>
-      <c r="H54">
-        <f t="shared" si="2"/>
-        <v>0.3115917739240599</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.3104791124189194</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>45131</v>
       </c>
@@ -14617,23 +14585,18 @@
       <c r="D55">
         <v>5585.35</v>
       </c>
-      <c r="E55">
-        <v>232.72291666666669</v>
-      </c>
-      <c r="F55">
+      <c r="I55">
+        <v>0.4363344865412202</v>
+      </c>
+      <c r="J55">
+        <v>0.69408940780249473</v>
+      </c>
+      <c r="K55">
         <f t="shared" si="0"/>
-        <v>0.43673986486486488</v>
-      </c>
-      <c r="G55">
-        <f t="shared" si="1"/>
-        <v>0.69593025362318839</v>
-      </c>
-      <c r="H55">
-        <f t="shared" si="2"/>
-        <v>0.30394048492276243</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.30285514536720115</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>45138</v>
       </c>
@@ -14646,23 +14609,18 @@
       <c r="D56">
         <v>5539.7999999999993</v>
       </c>
-      <c r="E56">
-        <v>230.82499999999996</v>
-      </c>
-      <c r="F56">
+      <c r="I56">
+        <v>0.39853176947093077</v>
+      </c>
+      <c r="J56">
+        <v>0.68977476403162619</v>
+      </c>
+      <c r="K56">
         <f t="shared" si="0"/>
-        <v>0.39890202702702704</v>
-      </c>
-      <c r="G56">
-        <f t="shared" si="1"/>
-        <v>0.69160416666666658</v>
-      </c>
-      <c r="H56">
-        <f t="shared" si="2"/>
-        <v>0.27588230398367114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.27489715724591773</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>45145</v>
       </c>
@@ -14675,23 +14633,18 @@
       <c r="D57">
         <v>5533.125</v>
       </c>
-      <c r="E57">
-        <v>230.546875</v>
-      </c>
-      <c r="F57">
+      <c r="I57">
+        <v>0.40486034933760867</v>
+      </c>
+      <c r="J57">
+        <v>0.69163486694708232</v>
+      </c>
+      <c r="K57">
         <f t="shared" si="0"/>
-        <v>0.40523648648648647</v>
-      </c>
-      <c r="G57">
-        <f t="shared" si="1"/>
-        <v>0.69346920289855074</v>
-      </c>
-      <c r="H57">
-        <f t="shared" si="2"/>
-        <v>0.28101902326919309</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.28001553384626626</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>45152</v>
       </c>
@@ -14704,23 +14657,18 @@
       <c r="D58">
         <v>5465.7749999999996</v>
       </c>
-      <c r="E58">
-        <v>227.74062499999999</v>
-      </c>
-      <c r="F58">
+      <c r="I58">
+        <v>0.50890220234579364</v>
+      </c>
+      <c r="J58">
+        <v>0.69583387537400809</v>
+      </c>
+      <c r="K58">
         <f t="shared" si="0"/>
-        <v>0.50937500000000002</v>
-      </c>
-      <c r="G58">
-        <f t="shared" si="1"/>
-        <v>0.69767934782608698</v>
-      </c>
-      <c r="H58">
-        <f t="shared" si="2"/>
-        <v>0.35538041779891305</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.35411139164464123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>45159</v>
       </c>
@@ -14733,23 +14681,18 @@
       <c r="D59">
         <v>5405.2750000000005</v>
       </c>
-      <c r="E59">
-        <v>225.21979166666668</v>
-      </c>
-      <c r="F59">
+      <c r="I59">
+        <v>0.51193992068179905</v>
+      </c>
+      <c r="J59">
+        <v>0.72062320223176202</v>
+      </c>
+      <c r="K59">
         <f t="shared" si="0"/>
-        <v>0.51241554054054061</v>
-      </c>
-      <c r="G59">
-        <f t="shared" si="1"/>
-        <v>0.72253442028985504</v>
-      </c>
-      <c r="H59">
-        <f t="shared" si="2"/>
-        <v>0.37023786553197224</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.36891578499199229</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>45166</v>
       </c>
@@ -14762,23 +14705,18 @@
       <c r="D60">
         <v>5497.9500000000007</v>
       </c>
-      <c r="E60">
-        <v>229.08125000000004</v>
-      </c>
-      <c r="F60">
+      <c r="I60">
+        <v>0.45413889123280743</v>
+      </c>
+      <c r="J60">
+        <v>0.74949680557362353</v>
+      </c>
+      <c r="K60">
         <f t="shared" si="0"/>
-        <v>0.45456081081081084</v>
-      </c>
-      <c r="G60">
-        <f t="shared" si="1"/>
-        <v>0.75148460144927542</v>
-      </c>
-      <c r="H60">
-        <f t="shared" si="2"/>
-        <v>0.34159544974662165</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.34037564826573641</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>45173</v>
       </c>
@@ -14791,23 +14729,18 @@
       <c r="D61">
         <v>5452.4250000000002</v>
       </c>
-      <c r="E61">
-        <v>227.18437500000002</v>
-      </c>
-      <c r="F61">
+      <c r="I61">
+        <v>0.39912243692515403</v>
+      </c>
+      <c r="J61">
+        <v>0.76575802581559049</v>
+      </c>
+      <c r="K61">
         <f t="shared" si="0"/>
-        <v>0.39949324324324326</v>
-      </c>
-      <c r="G61">
-        <f t="shared" si="1"/>
-        <v>0.76778894927536234</v>
-      </c>
-      <c r="H61">
-        <f t="shared" si="2"/>
-        <v>0.30672649747233649</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.30563120935851351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>45180</v>
       </c>
@@ -14820,23 +14753,18 @@
       <c r="D62">
         <v>5388.05</v>
       </c>
-      <c r="E62">
-        <v>224.50208333333333</v>
-      </c>
-      <c r="F62">
+      <c r="I62">
+        <v>0.36747953759176444</v>
+      </c>
+      <c r="J62">
+        <v>0.78574667909746609</v>
+      </c>
+      <c r="K62">
         <f t="shared" si="0"/>
-        <v>0.36782094594594594</v>
-      </c>
-      <c r="G62">
-        <f t="shared" si="1"/>
-        <v>0.78783061594202897</v>
-      </c>
-      <c r="H62">
-        <f t="shared" si="2"/>
-        <v>0.28978060240097431</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.28874582629900136</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>45187</v>
       </c>
@@ -14849,23 +14777,18 @@
       <c r="D63">
         <v>5193.6750000000002</v>
       </c>
-      <c r="E63">
-        <v>216.40312500000002</v>
-      </c>
-      <c r="F63">
+      <c r="I63">
+        <v>0.35802885832419207</v>
+      </c>
+      <c r="J63">
+        <v>0.80524839917320723</v>
+      </c>
+      <c r="K63">
         <f t="shared" si="0"/>
-        <v>0.35836148648648647</v>
-      </c>
-      <c r="G63">
-        <f t="shared" si="1"/>
-        <v>0.80738405797101442</v>
-      </c>
-      <c r="H63">
-        <f t="shared" si="2"/>
-        <v>0.28933535117998427</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.2883021650233667</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>45194</v>
       </c>
@@ -14878,23 +14801,18 @@
       <c r="D64">
         <v>5278.4250000000002</v>
       </c>
-      <c r="E64">
-        <v>219.93437500000002</v>
-      </c>
-      <c r="F64">
+      <c r="I64">
+        <v>0.34866256012150876</v>
+      </c>
+      <c r="J64">
+        <v>0.83501456282612774</v>
+      </c>
+      <c r="K64">
         <f t="shared" si="0"/>
-        <v>0.3489864864864865</v>
-      </c>
-      <c r="G64">
-        <f t="shared" si="1"/>
-        <v>0.83722916666666669</v>
-      </c>
-      <c r="H64">
-        <f t="shared" si="2"/>
-        <v>0.29218166525900902</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.29113831521370009</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>45201</v>
       </c>
@@ -14907,23 +14825,18 @@
       <c r="D65">
         <v>5413.7249999999995</v>
       </c>
-      <c r="E65">
-        <v>225.57187499999998</v>
-      </c>
-      <c r="F65">
+      <c r="I65">
+        <v>0.4280651421820944</v>
+      </c>
+      <c r="J65">
+        <v>0.84129049043840243</v>
+      </c>
+      <c r="K65">
         <f t="shared" si="0"/>
-        <v>0.42846283783783784</v>
-      </c>
-      <c r="G65">
-        <f t="shared" si="1"/>
-        <v>0.84352173913043482</v>
-      </c>
-      <c r="H65">
-        <f t="shared" si="2"/>
-        <v>0.36141771812573442</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.36012713340595864</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>45208</v>
       </c>
@@ -14936,23 +14849,18 @@
       <c r="D66">
         <v>5474.9500000000007</v>
       </c>
-      <c r="E66">
-        <v>228.1229166666667</v>
-      </c>
-      <c r="F66">
+      <c r="I66">
+        <v>0.44823221669057473</v>
+      </c>
+      <c r="J66">
+        <v>0.85782995822673191</v>
+      </c>
+      <c r="K66">
         <f t="shared" si="0"/>
-        <v>0.44864864864864867</v>
-      </c>
-      <c r="G66">
-        <f t="shared" si="1"/>
-        <v>0.86010507246376811</v>
-      </c>
-      <c r="H66">
-        <f t="shared" si="2"/>
-        <v>0.3858849784567176</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.38450702371955114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>45215</v>
       </c>
@@ -14965,23 +14873,18 @@
       <c r="D67">
         <v>5425.5</v>
       </c>
-      <c r="E67">
-        <v>226.0625</v>
-      </c>
-      <c r="F67">
-        <f t="shared" ref="F67:F130" si="3">B67/296</f>
-        <v>0.33868243243243246</v>
-      </c>
-      <c r="G67">
-        <f t="shared" ref="G67:G130" si="4">(C67/1000)/276</f>
-        <v>0.85104076086956515</v>
-      </c>
-      <c r="H67">
-        <f t="shared" ref="H67:H130" si="5">F67*G67</f>
-        <v>0.28823255499045242</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67">
+        <v>0.338368070205046</v>
+      </c>
+      <c r="J67">
+        <v>0.84878962317332285</v>
+      </c>
+      <c r="K67">
+        <f t="shared" ref="K67:K130" si="1">I67*J67</f>
+        <v>0.28720330680322542</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>45222</v>
       </c>
@@ -14994,23 +14897,18 @@
       <c r="D68">
         <v>5459.9</v>
       </c>
-      <c r="E68">
-        <v>227.49583333333331</v>
-      </c>
-      <c r="F68">
-        <f t="shared" si="3"/>
-        <v>0.53057432432432439</v>
-      </c>
-      <c r="G68">
-        <f t="shared" si="4"/>
-        <v>0.83221286231884062</v>
-      </c>
-      <c r="H68">
-        <f t="shared" si="5"/>
-        <v>0.44155077711883084</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68">
+        <v>0.53008184963294247</v>
+      </c>
+      <c r="J68">
+        <v>0.83001152739834927</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="1"/>
+        <v>0.43997404565998066</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>45229</v>
       </c>
@@ -15023,23 +14921,18 @@
       <c r="D69">
         <v>5597.85</v>
       </c>
-      <c r="E69">
-        <v>233.24375000000001</v>
-      </c>
-      <c r="F69">
-        <f t="shared" si="3"/>
-        <v>0.63597972972972971</v>
-      </c>
-      <c r="G69">
-        <f t="shared" si="4"/>
-        <v>0.79769836956521734</v>
-      </c>
-      <c r="H69">
-        <f t="shared" si="5"/>
-        <v>0.50731999348193302</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69">
+        <v>0.63538941861446296</v>
+      </c>
+      <c r="J69">
+        <v>0.79558833094835424</v>
+      </c>
+      <c r="K69">
+        <f t="shared" si="1"/>
+        <v>0.50550840705772571</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>45236</v>
       </c>
@@ -15052,23 +14945,18 @@
       <c r="D70">
         <v>5851.3499999999995</v>
       </c>
-      <c r="E70">
-        <v>243.80624999999998</v>
-      </c>
-      <c r="F70">
-        <f t="shared" si="3"/>
-        <v>0.64349662162162158</v>
-      </c>
-      <c r="G70">
-        <f t="shared" si="4"/>
-        <v>0.79178804347826093</v>
-      </c>
-      <c r="H70">
-        <f t="shared" si="5"/>
-        <v>0.50951293101865458</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70">
+        <v>0.64289933338958738</v>
+      </c>
+      <c r="J70">
+        <v>0.78969363861064124</v>
+      </c>
+      <c r="K70">
+        <f t="shared" si="1"/>
+        <v>0.50769351384477901</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>45243</v>
       </c>
@@ -15081,23 +14969,18 @@
       <c r="D71">
         <v>6141.1750000000002</v>
       </c>
-      <c r="E71">
-        <v>255.88229166666667</v>
-      </c>
-      <c r="F71">
-        <f t="shared" si="3"/>
-        <v>0.68032094594594594</v>
-      </c>
-      <c r="G71">
-        <f t="shared" si="4"/>
-        <v>0.82056702898550715</v>
-      </c>
-      <c r="H71">
-        <f t="shared" si="5"/>
-        <v>0.55824893737147463</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71">
+        <v>0.67968947768120835</v>
+      </c>
+      <c r="J71">
+        <v>0.81839649913996204</v>
+      </c>
+      <c r="K71">
+        <f t="shared" si="1"/>
+        <v>0.55625548903657029</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>45250</v>
       </c>
@@ -15110,23 +14993,18 @@
       <c r="D72">
         <v>6097.05</v>
       </c>
-      <c r="E72">
-        <v>254.04375000000002</v>
-      </c>
-      <c r="F72">
-        <f t="shared" si="3"/>
-        <v>0.59991554054054053</v>
-      </c>
-      <c r="G72">
-        <f t="shared" si="4"/>
-        <v>0.81099094202898547</v>
-      </c>
-      <c r="H72">
-        <f t="shared" si="5"/>
-        <v>0.48652606936080101</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72">
+        <v>0.59935870390684332</v>
+      </c>
+      <c r="J72">
+        <v>0.80884574245118013</v>
+      </c>
+      <c r="K72">
+        <f t="shared" si="1"/>
+        <v>0.48478873585610771</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>45257</v>
       </c>
@@ -15139,23 +15017,18 @@
       <c r="D73">
         <v>5975.55</v>
       </c>
-      <c r="E73">
-        <v>248.98125000000002</v>
-      </c>
-      <c r="F73">
-        <f t="shared" si="3"/>
-        <v>0.56486486486486487</v>
-      </c>
-      <c r="G73">
-        <f t="shared" si="4"/>
-        <v>0.81750362318840575</v>
-      </c>
-      <c r="H73">
-        <f t="shared" si="5"/>
-        <v>0.46177907363885623</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73">
+        <v>0.56434056197789217</v>
+      </c>
+      <c r="J73">
+        <v>0.81534119653672132</v>
+      </c>
+      <c r="K73">
+        <f t="shared" si="1"/>
+        <v>0.46013010905726037</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>45264</v>
       </c>
@@ -15168,23 +15041,18 @@
       <c r="D74">
         <v>5768.5999999999995</v>
       </c>
-      <c r="E74">
-        <v>240.35833333333332</v>
-      </c>
-      <c r="F74">
-        <f t="shared" si="3"/>
-        <v>0.44248310810810809</v>
-      </c>
-      <c r="G74">
-        <f t="shared" si="4"/>
-        <v>0.82071648550724641</v>
-      </c>
-      <c r="H74">
-        <f t="shared" si="5"/>
-        <v>0.36315318138280944</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74">
+        <v>0.44207239895367478</v>
+      </c>
+      <c r="J74">
+        <v>0.8185455603255134</v>
+      </c>
+      <c r="K74">
+        <f t="shared" si="1"/>
+        <v>0.36185639950597964</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>45271</v>
       </c>
@@ -15197,23 +15065,18 @@
       <c r="D75">
         <v>5910.125</v>
       </c>
-      <c r="E75">
-        <v>246.25520833333334</v>
-      </c>
-      <c r="F75">
-        <f t="shared" si="3"/>
-        <v>0.43809121621621627</v>
-      </c>
-      <c r="G75">
-        <f t="shared" si="4"/>
-        <v>0.81291304347826088</v>
-      </c>
-      <c r="H75">
-        <f t="shared" si="5"/>
-        <v>0.35613006389541718</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75">
+        <v>0.43768458357944484</v>
+      </c>
+      <c r="J75">
+        <v>0.81076275963748312</v>
+      </c>
+      <c r="K75">
+        <f t="shared" si="1"/>
+        <v>0.35485836083365335</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>45278</v>
       </c>
@@ -15226,23 +15089,18 @@
       <c r="D76">
         <v>5991.6750000000002</v>
       </c>
-      <c r="E76">
-        <v>249.65312500000002</v>
-      </c>
-      <c r="F76">
-        <f t="shared" si="3"/>
-        <v>0.39805743243243247</v>
-      </c>
-      <c r="G76">
-        <f t="shared" si="4"/>
-        <v>0.81878079710144924</v>
-      </c>
-      <c r="H76">
-        <f t="shared" si="5"/>
-        <v>0.32592178181918335</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76">
+        <v>0.39768795882204039</v>
+      </c>
+      <c r="J76">
+        <v>0.81661499212234212</v>
+      </c>
+      <c r="K76">
+        <f t="shared" si="1"/>
+        <v>0.32475794936061081</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>45285</v>
       </c>
@@ -15255,23 +15113,18 @@
       <c r="D77">
         <v>6104.9</v>
       </c>
-      <c r="E77">
-        <v>254.37083333333331</v>
-      </c>
-      <c r="F77">
-        <f t="shared" si="3"/>
-        <v>0.31849662162162157</v>
-      </c>
-      <c r="G77">
-        <f t="shared" si="4"/>
-        <v>0.82005525362318843</v>
-      </c>
-      <c r="H77">
-        <f t="shared" si="5"/>
-        <v>0.26118482782204755</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77">
+        <v>0.31820099569656568</v>
+      </c>
+      <c r="J77">
+        <v>0.81788607750458919</v>
+      </c>
+      <c r="K77">
+        <f t="shared" si="1"/>
+        <v>0.26025216422831876</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>45292</v>
       </c>
@@ -15284,23 +15137,18 @@
       <c r="D78">
         <v>5967.9250000000002</v>
       </c>
-      <c r="E78">
-        <v>248.66354166666667</v>
-      </c>
-      <c r="F78">
-        <f t="shared" si="3"/>
-        <v>0.19957770270270273</v>
-      </c>
-      <c r="G78">
-        <f t="shared" si="4"/>
-        <v>0.87923188405797104</v>
-      </c>
-      <c r="H78">
-        <f t="shared" si="5"/>
-        <v>0.17547507956325895</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78">
+        <v>0.19939245633279895</v>
+      </c>
+      <c r="J78">
+        <v>0.87690617637280832</v>
+      </c>
+      <c r="K78">
+        <f t="shared" si="1"/>
+        <v>0.17484847648037688</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>45299</v>
       </c>
@@ -15313,23 +15161,18 @@
       <c r="D79">
         <v>5784.7</v>
       </c>
-      <c r="E79">
-        <v>241.02916666666667</v>
-      </c>
-      <c r="F79">
-        <f t="shared" si="3"/>
-        <v>0.2189189189189189</v>
-      </c>
-      <c r="G79">
-        <f t="shared" si="4"/>
-        <v>0.91500905797101451</v>
-      </c>
-      <c r="H79">
-        <f t="shared" si="5"/>
-        <v>0.2003127937720329</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79">
+        <v>0.21871572019238883</v>
+      </c>
+      <c r="J79">
+        <v>0.91258871399043107</v>
+      </c>
+      <c r="K79">
+        <f t="shared" si="1"/>
+        <v>0.19959749781986308</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>45306</v>
       </c>
@@ -15342,23 +15185,18 @@
       <c r="D80">
         <v>5765.375</v>
       </c>
-      <c r="E80">
-        <v>240.22395833333334</v>
-      </c>
-      <c r="F80">
-        <f t="shared" si="3"/>
-        <v>0.18243243243243243</v>
-      </c>
-      <c r="G80">
-        <f t="shared" si="4"/>
-        <v>0.92127083333333326</v>
-      </c>
-      <c r="H80">
-        <f t="shared" si="5"/>
-        <v>0.16806967905405404</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80">
+        <v>0.18226310016032404</v>
+      </c>
+      <c r="J80">
+        <v>0.91883392596447089</v>
+      </c>
+      <c r="K80">
+        <f t="shared" si="1"/>
+        <v>0.16746951987876613</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>45313</v>
       </c>
@@ -15371,23 +15209,18 @@
       <c r="D81">
         <v>5840.5749999999998</v>
       </c>
-      <c r="E81">
-        <v>243.35729166666667</v>
-      </c>
-      <c r="F81">
-        <f t="shared" si="3"/>
-        <v>0.18243243243243243</v>
-      </c>
-      <c r="G81">
-        <f t="shared" si="4"/>
-        <v>0.96749637681159417</v>
-      </c>
-      <c r="H81">
-        <f t="shared" si="5"/>
-        <v>0.17650271739130433</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81">
+        <v>0.18226310016032404</v>
+      </c>
+      <c r="J81">
+        <v>0.96493719555382096</v>
+      </c>
+      <c r="K81">
+        <f t="shared" si="1"/>
+        <v>0.17587244472164826</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>45320</v>
       </c>
@@ -15400,23 +15233,18 @@
       <c r="D82">
         <v>6144.25</v>
       </c>
-      <c r="E82">
-        <v>256.01041666666669</v>
-      </c>
-      <c r="F82">
-        <f t="shared" si="3"/>
-        <v>0.21444256756756752</v>
-      </c>
-      <c r="G82">
-        <f t="shared" si="4"/>
-        <v>0.96168387681159428</v>
-      </c>
-      <c r="H82">
-        <f t="shared" si="5"/>
-        <v>0.2062259597318106</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82">
+        <v>0.21424352375326974</v>
+      </c>
+      <c r="J82">
+        <v>0.95914007053755979</v>
+      </c>
+      <c r="K82">
+        <f t="shared" si="1"/>
+        <v>0.20548954848492651</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>45327</v>
       </c>
@@ -15429,23 +15257,18 @@
       <c r="D83">
         <v>5978.125</v>
       </c>
-      <c r="E83">
-        <v>249.08854166666666</v>
-      </c>
-      <c r="F83">
-        <f t="shared" si="3"/>
-        <v>0.27905405405405403</v>
-      </c>
-      <c r="G83">
-        <f t="shared" si="4"/>
-        <v>0.93564945652173925</v>
-      </c>
-      <c r="H83">
-        <f t="shared" si="5"/>
-        <v>0.26109677401586373</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83">
+        <v>0.27879503839338454</v>
+      </c>
+      <c r="J83">
+        <v>0.93317451541563678</v>
+      </c>
+      <c r="K83">
+        <f t="shared" si="1"/>
+        <v>0.26016442485303048</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>45334</v>
       </c>
@@ -15458,23 +15281,18 @@
       <c r="D84">
         <v>5943.55</v>
       </c>
-      <c r="E84">
-        <v>247.64791666666667</v>
-      </c>
-      <c r="F84">
-        <f t="shared" si="3"/>
-        <v>0.18826013513513509</v>
-      </c>
-      <c r="G84">
-        <f t="shared" si="4"/>
-        <v>0.95266938405797108</v>
-      </c>
-      <c r="H84">
-        <f t="shared" si="5"/>
-        <v>0.17934966698185956</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84">
+        <v>0.18808539363766769</v>
+      </c>
+      <c r="J84">
+        <v>0.9501494225460011</v>
+      </c>
+      <c r="K84">
+        <f t="shared" si="1"/>
+        <v>0.17870922815416726</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>45341</v>
       </c>
@@ -15487,23 +15305,18 @@
       <c r="D85">
         <v>5770.375</v>
       </c>
-      <c r="E85">
-        <v>240.43229166666666</v>
-      </c>
-      <c r="F85">
-        <f t="shared" si="3"/>
-        <v>0.14653716216216217</v>
-      </c>
-      <c r="G85">
-        <f t="shared" si="4"/>
-        <v>1.0026521739130436</v>
-      </c>
-      <c r="H85">
-        <f t="shared" si="5"/>
-        <v>0.14692580420094009</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85">
+        <v>0.14640114758248252</v>
+      </c>
+      <c r="J85">
+        <v>1</v>
+      </c>
+      <c r="K85">
+        <f t="shared" si="1"/>
+        <v>0.14640114758248252</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>45348</v>
       </c>
@@ -15516,23 +15329,18 @@
       <c r="D86">
         <v>5726.0250000000005</v>
       </c>
-      <c r="E86">
-        <v>238.58437500000002</v>
-      </c>
-      <c r="F86">
-        <f t="shared" si="3"/>
-        <v>0.15160472972972974</v>
-      </c>
-      <c r="G86">
-        <f t="shared" si="4"/>
-        <v>0.98495833333333338</v>
-      </c>
-      <c r="H86">
-        <f t="shared" si="5"/>
-        <v>0.14932434192004507</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86">
+        <v>0.15146401147582483</v>
+      </c>
+      <c r="J86">
+        <v>0.98235296243296755</v>
+      </c>
+      <c r="K86">
+        <f t="shared" si="1"/>
+        <v>0.14879112037525752</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>45355</v>
       </c>
@@ -15545,23 +15353,18 @@
       <c r="D87">
         <v>5958.3</v>
       </c>
-      <c r="E87">
-        <v>248.26250000000002</v>
-      </c>
-      <c r="F87">
-        <f t="shared" si="3"/>
-        <v>0.12922297297297297</v>
-      </c>
-      <c r="G87">
-        <f t="shared" si="4"/>
-        <v>0.94422373188405795</v>
-      </c>
-      <c r="H87">
-        <f t="shared" si="5"/>
-        <v>0.1220153977856933</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87">
+        <v>0.12910302928022951</v>
+      </c>
+      <c r="J87">
+        <v>0.94172611046066224</v>
+      </c>
+      <c r="K87">
+        <f t="shared" si="1"/>
+        <v>0.12157969361275953</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>45362</v>
       </c>
@@ -15574,23 +15377,18 @@
       <c r="D88">
         <v>6193.5749999999998</v>
       </c>
-      <c r="E88">
-        <v>258.06562500000001</v>
-      </c>
-      <c r="F88">
-        <f t="shared" si="3"/>
-        <v>0.12550675675675677</v>
-      </c>
-      <c r="G88">
-        <f t="shared" si="4"/>
-        <v>0.89690489130434781</v>
-      </c>
-      <c r="H88">
-        <f t="shared" si="5"/>
-        <v>0.11256762402688014</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88">
+        <v>0.12539026242511181</v>
+      </c>
+      <c r="J88">
+        <v>0.89453243571397589</v>
+      </c>
+      <c r="K88">
+        <f t="shared" si="1"/>
+        <v>0.1121656568619499</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>45369</v>
       </c>
@@ -15603,23 +15401,18 @@
       <c r="D89">
         <v>6439.4750000000004</v>
       </c>
-      <c r="E89">
-        <v>268.31145833333335</v>
-      </c>
-      <c r="F89">
-        <f t="shared" si="3"/>
-        <v>0.13108108108108107</v>
-      </c>
-      <c r="G89">
-        <f t="shared" si="4"/>
-        <v>0.88394836956521738</v>
-      </c>
-      <c r="H89">
-        <f t="shared" si="5"/>
-        <v>0.11586890790246768</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89">
+        <v>0.13095941270778838</v>
+      </c>
+      <c r="J89">
+        <v>0.8816101860283595</v>
+      </c>
+      <c r="K89">
+        <f t="shared" si="1"/>
+        <v>0.11545515219947802</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>45376</v>
       </c>
@@ -15632,23 +15425,18 @@
       <c r="D90">
         <v>6316.9250000000002</v>
       </c>
-      <c r="E90">
-        <v>263.20520833333336</v>
-      </c>
-      <c r="F90">
-        <f t="shared" si="3"/>
-        <v>0.13547297297297298</v>
-      </c>
-      <c r="G90">
-        <f t="shared" si="4"/>
-        <v>0.85245652173913045</v>
-      </c>
-      <c r="H90">
-        <f t="shared" si="5"/>
-        <v>0.11548481933019977</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90">
+        <v>0.13534722808201841</v>
+      </c>
+      <c r="J90">
+        <v>0.85020163913100022</v>
+      </c>
+      <c r="K90">
+        <f t="shared" si="1"/>
+        <v>0.11507243516716939</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>45383</v>
       </c>
@@ -15661,23 +15449,18 @@
       <c r="D91">
         <v>6429.25</v>
       </c>
-      <c r="E91">
-        <v>267.88541666666669</v>
-      </c>
-      <c r="F91">
-        <f t="shared" si="3"/>
-        <v>6.3682432432432434E-2</v>
-      </c>
-      <c r="G91">
-        <f t="shared" si="4"/>
-        <v>0.84492663043478256</v>
-      </c>
-      <c r="H91">
-        <f t="shared" si="5"/>
-        <v>5.380698305302585E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I91">
+        <v>6.3623322926335338E-2</v>
+      </c>
+      <c r="J91">
+        <v>0.84269166558258524</v>
+      </c>
+      <c r="K91">
+        <f t="shared" si="1"/>
+        <v>5.3614843966692208E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>45390</v>
       </c>
@@ -15690,23 +15473,18 @@
       <c r="D92">
         <v>6472.55</v>
       </c>
-      <c r="E92">
-        <v>269.68958333333336</v>
-      </c>
-      <c r="F92">
-        <f t="shared" si="3"/>
-        <v>6.3682432432432434E-2</v>
-      </c>
-      <c r="G92">
-        <f t="shared" si="4"/>
-        <v>0.8803405797101449</v>
-      </c>
-      <c r="H92">
-        <f t="shared" si="5"/>
-        <v>5.60622294849197E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I92">
+        <v>6.3623322926335338E-2</v>
+      </c>
+      <c r="J92">
+        <v>0.87801193934926203</v>
+      </c>
+      <c r="K92">
+        <f t="shared" si="1"/>
+        <v>5.5862037150396053E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>45397</v>
       </c>
@@ -15719,23 +15497,18 @@
       <c r="D93">
         <v>6675.2250000000004</v>
       </c>
-      <c r="E93">
-        <v>278.13437500000003</v>
-      </c>
-      <c r="F93">
-        <f t="shared" si="3"/>
-        <v>0.14417229729729727</v>
-      </c>
-      <c r="G93">
-        <f t="shared" si="4"/>
-        <v>0.85549547101449275</v>
-      </c>
-      <c r="H93">
-        <f t="shared" si="5"/>
-        <v>0.12333874738359281</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I93">
+        <v>0.1440384777655894</v>
+      </c>
+      <c r="J93">
+        <v>0.85323254990387798</v>
+      </c>
+      <c r="K93">
+        <f t="shared" si="1"/>
+        <v>0.12289831766820687</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>45404</v>
       </c>
@@ -15748,23 +15521,18 @@
       <c r="D94">
         <v>6896.7749999999996</v>
       </c>
-      <c r="E94">
-        <v>287.36562499999997</v>
-      </c>
-      <c r="F94">
-        <f t="shared" si="3"/>
-        <v>0.20185810810810811</v>
-      </c>
-      <c r="G94">
-        <f t="shared" si="4"/>
-        <v>0.81015851449275356</v>
-      </c>
-      <c r="H94">
-        <f t="shared" si="5"/>
-        <v>0.16353706500318252</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I94">
+        <v>0.20167074508480298</v>
+      </c>
+      <c r="J94">
+        <v>0.80801551681771522</v>
+      </c>
+      <c r="K94">
+        <f t="shared" si="1"/>
+        <v>0.16295309131671079</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>45411</v>
       </c>
@@ -15777,23 +15545,18 @@
       <c r="D95">
         <v>6802.625</v>
       </c>
-      <c r="E95">
-        <v>283.44270833333331</v>
-      </c>
-      <c r="F95">
-        <f t="shared" si="3"/>
-        <v>0.29847972972972969</v>
-      </c>
-      <c r="G95">
-        <f t="shared" si="4"/>
-        <v>0.78769384057971015</v>
-      </c>
-      <c r="H95">
-        <f t="shared" si="5"/>
-        <v>0.23511064464600467</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I95">
+        <v>0.29820268331786348</v>
+      </c>
+      <c r="J95">
+        <v>0.78561026552765845</v>
+      </c>
+      <c r="K95">
+        <f t="shared" si="1"/>
+        <v>0.23427108922240697</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>45418</v>
       </c>
@@ -15806,23 +15569,18 @@
       <c r="D96">
         <v>6853.2250000000004</v>
       </c>
-      <c r="E96">
-        <v>285.55104166666666</v>
-      </c>
-      <c r="F96">
-        <f t="shared" si="3"/>
-        <v>0.44070945945945944</v>
-      </c>
-      <c r="G96">
-        <f t="shared" si="4"/>
-        <v>0.78101539855072466</v>
-      </c>
-      <c r="H96">
-        <f t="shared" si="5"/>
-        <v>0.34420087412480416</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I96">
+        <v>0.44030039659100495</v>
+      </c>
+      <c r="J96">
+        <v>0.77894948903632388</v>
+      </c>
+      <c r="K96">
+        <f t="shared" si="1"/>
+        <v>0.34297176894705406</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>45425</v>
       </c>
@@ -15835,23 +15593,18 @@
       <c r="D97">
         <v>6787.7749999999996</v>
       </c>
-      <c r="E97">
-        <v>282.82395833333334</v>
-      </c>
-      <c r="F97">
-        <f t="shared" si="3"/>
-        <v>0.46798986486486488</v>
-      </c>
-      <c r="G97">
-        <f t="shared" si="4"/>
-        <v>0.78025090579710155</v>
-      </c>
-      <c r="H97">
-        <f t="shared" si="5"/>
-        <v>0.36514951596467399</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I97">
+        <v>0.4675554805501646</v>
+      </c>
+      <c r="J97">
+        <v>0.77818701848720062</v>
+      </c>
+      <c r="K97">
+        <f t="shared" si="1"/>
+        <v>0.36384560538668292</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>45432</v>
       </c>
@@ -15864,23 +15617,18 @@
       <c r="D98">
         <v>6845.4750000000004</v>
       </c>
-      <c r="E98">
-        <v>285.22812500000003</v>
-      </c>
-      <c r="F98">
-        <f t="shared" si="3"/>
-        <v>0.47846283783783783</v>
-      </c>
-      <c r="G98">
-        <f t="shared" si="4"/>
-        <v>0.73692481884057981</v>
-      </c>
-      <c r="H98">
-        <f t="shared" si="5"/>
-        <v>0.35259114009559833</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I98">
+        <v>0.47801873259640543</v>
+      </c>
+      <c r="J98">
+        <v>0.73497553589754705</v>
+      </c>
+      <c r="K98">
+        <f t="shared" si="1"/>
+        <v>0.35133207415910933</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>45439</v>
       </c>
@@ -15893,23 +15641,18 @@
       <c r="D99">
         <v>6890.625</v>
       </c>
-      <c r="E99">
-        <v>287.109375</v>
-      </c>
-      <c r="F99">
-        <f t="shared" si="3"/>
-        <v>0.546875</v>
-      </c>
-      <c r="G99">
-        <f t="shared" si="4"/>
-        <v>0.73395471014492752</v>
-      </c>
-      <c r="H99">
-        <f t="shared" si="5"/>
-        <v>0.40138148211050723</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I99">
+        <v>0.54636739515652688</v>
+      </c>
+      <c r="J99">
+        <v>0.73201328361013529</v>
+      </c>
+      <c r="K99">
+        <f t="shared" si="1"/>
+        <v>0.39994819098604556</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>45446</v>
       </c>
@@ -15922,23 +15665,18 @@
       <c r="D100">
         <v>6881.15</v>
       </c>
-      <c r="E100">
-        <v>286.71458333333334</v>
-      </c>
-      <c r="F100">
-        <f t="shared" si="3"/>
-        <v>0.60278716216216222</v>
-      </c>
-      <c r="G100">
-        <f t="shared" si="4"/>
-        <v>0.7191757246376812</v>
-      </c>
-      <c r="H100">
-        <f t="shared" si="5"/>
-        <v>0.43350989415026447</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I100">
+        <v>0.60222766011307072</v>
+      </c>
+      <c r="J100">
+        <v>0.71727339086191688</v>
+      </c>
+      <c r="K100">
+        <f t="shared" si="1"/>
+        <v>0.43196187584014023</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>45453</v>
       </c>
@@ -15951,23 +15689,18 @@
       <c r="D101">
         <v>6320.9250000000002</v>
       </c>
-      <c r="E101">
-        <v>263.37187499999999</v>
-      </c>
-      <c r="F101">
-        <f t="shared" si="3"/>
-        <v>0.68184121621621618</v>
-      </c>
-      <c r="G101">
-        <f t="shared" si="4"/>
-        <v>0.62941304347826088</v>
-      </c>
-      <c r="H101">
-        <f t="shared" si="5"/>
-        <v>0.42915975506756754</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I101">
+        <v>0.681208336849211</v>
+      </c>
+      <c r="J101">
+        <v>0.62774814622089237</v>
+      </c>
+      <c r="K101">
+        <f t="shared" si="1"/>
+        <v>0.42762727064730943</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>45460</v>
       </c>
@@ -15980,23 +15713,18 @@
       <c r="D102">
         <v>6025.375</v>
       </c>
-      <c r="E102">
-        <v>251.05729166666666</v>
-      </c>
-      <c r="F102">
-        <f t="shared" si="3"/>
-        <v>0.66967905405405403</v>
-      </c>
-      <c r="G102">
-        <f t="shared" si="4"/>
-        <v>0.61950724637681165</v>
-      </c>
-      <c r="H102">
-        <f t="shared" si="5"/>
-        <v>0.41487102673325504</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I102">
+        <v>0.66905746350518946</v>
+      </c>
+      <c r="J102">
+        <v>0.61786855152277287</v>
+      </c>
+      <c r="K102">
+        <f t="shared" si="1"/>
+        <v>0.41338956586145187</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>45467</v>
       </c>
@@ -16009,23 +15737,18 @@
       <c r="D103">
         <v>5828.7250000000004</v>
       </c>
-      <c r="E103">
-        <v>242.86354166666669</v>
-      </c>
-      <c r="F103">
-        <f t="shared" si="3"/>
-        <v>0.60371621621621618</v>
-      </c>
-      <c r="G103">
-        <f t="shared" si="4"/>
-        <v>0.62078894927536232</v>
-      </c>
-      <c r="H103">
-        <f t="shared" si="5"/>
-        <v>0.37478035552536232</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I103">
+        <v>0.60315585182685005</v>
+      </c>
+      <c r="J103">
+        <v>0.61914686411401643</v>
+      </c>
+      <c r="K103">
+        <f t="shared" si="1"/>
+        <v>0.37344205423061255</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>45474</v>
       </c>
@@ -16038,23 +15761,18 @@
       <c r="D104">
         <v>5639.6</v>
       </c>
-      <c r="E104">
-        <v>234.98333333333335</v>
-      </c>
-      <c r="F104">
-        <f t="shared" si="3"/>
-        <v>0.58885135135135136</v>
-      </c>
-      <c r="G104">
-        <f t="shared" si="4"/>
-        <v>0.6233115942028985</v>
-      </c>
-      <c r="H104">
-        <f t="shared" si="5"/>
-        <v>0.36703787455934195</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I104">
+        <v>0.58830478440637934</v>
+      </c>
+      <c r="J104">
+        <v>0.62166283624589846</v>
+      </c>
+      <c r="K104">
+        <f t="shared" si="1"/>
+        <v>0.3657272208511016</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>45509</v>
       </c>
@@ -16067,23 +15785,18 @@
       <c r="D105">
         <v>4964.1750000000002</v>
       </c>
-      <c r="E105">
-        <v>206.84062500000002</v>
-      </c>
-      <c r="F105">
-        <f t="shared" si="3"/>
-        <v>0.52322635135135132</v>
-      </c>
-      <c r="G105">
-        <f t="shared" si="4"/>
-        <v>0.63708514492753621</v>
-      </c>
-      <c r="H105">
-        <f t="shared" si="5"/>
-        <v>0.33333973588058163</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I105">
+        <v>0.52274069698759607</v>
+      </c>
+      <c r="J105">
+        <v>0.63539995374586233</v>
+      </c>
+      <c r="K105">
+        <f t="shared" si="1"/>
+        <v>0.33214941468699838</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>45516</v>
       </c>
@@ -16096,23 +15809,18 @@
       <c r="D106">
         <v>4795.25</v>
       </c>
-      <c r="E106">
-        <v>199.80208333333334</v>
-      </c>
-      <c r="F106">
-        <f t="shared" si="3"/>
-        <v>0.44712837837837838</v>
-      </c>
-      <c r="G106">
-        <f t="shared" si="4"/>
-        <v>0.64803260869565216</v>
-      </c>
-      <c r="H106">
-        <f t="shared" si="5"/>
-        <v>0.28975376946239717</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I106">
+        <v>0.44671335752257196</v>
+      </c>
+      <c r="J106">
+        <v>0.64631845973721858</v>
+      </c>
+      <c r="K106">
+        <f t="shared" si="1"/>
+        <v>0.28871908917803013</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>45523</v>
       </c>
@@ -16125,28 +15833,23 @@
       <c r="D107">
         <v>4585.375</v>
       </c>
-      <c r="E107">
-        <v>191.05729166666666</v>
-      </c>
-      <c r="F107">
-        <f t="shared" si="3"/>
-        <v>0.43395270270270264</v>
-      </c>
-      <c r="G107">
-        <f t="shared" si="4"/>
-        <v>0.63588768115942029</v>
-      </c>
-      <c r="H107">
-        <f t="shared" si="5"/>
-        <v>0.27594517785448486</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I107">
+        <v>0.43354991139988186</v>
+      </c>
+      <c r="J107">
+        <v>0.63420565745920232</v>
+      </c>
+      <c r="K107">
+        <f t="shared" si="1"/>
+        <v>0.27495980660074099</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>45530</v>
       </c>
       <c r="B108">
-        <v>94.899999999999991</v>
+        <v>94.9</v>
       </c>
       <c r="C108">
         <v>185839.75</v>
@@ -16154,23 +15857,18 @@
       <c r="D108">
         <v>4415.4750000000004</v>
       </c>
-      <c r="E108">
-        <v>183.97812500000001</v>
-      </c>
-      <c r="F108">
-        <f t="shared" si="3"/>
-        <v>0.32060810810810808</v>
-      </c>
-      <c r="G108">
-        <f t="shared" si="4"/>
-        <v>0.6733324275362319</v>
-      </c>
-      <c r="H108">
-        <f t="shared" si="5"/>
-        <v>0.21587583572023109</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I108">
+        <v>0.3203105223187917</v>
+      </c>
+      <c r="J108">
+        <v>0.67155135654712861</v>
+      </c>
+      <c r="K108">
+        <f t="shared" si="1"/>
+        <v>0.21510496577950389</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>45537</v>
       </c>
@@ -16183,28 +15881,23 @@
       <c r="D109">
         <v>4905.8249999999998</v>
       </c>
-      <c r="E109">
-        <v>204.40937499999998</v>
-      </c>
-      <c r="F109">
-        <f t="shared" si="3"/>
-        <v>0.28082770270270269</v>
-      </c>
-      <c r="G109">
-        <f t="shared" si="4"/>
-        <v>0.68613677536231887</v>
-      </c>
-      <c r="H109">
-        <f t="shared" si="5"/>
-        <v>0.19268621436484037</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I109">
+        <v>0.28056704075605438</v>
+      </c>
+      <c r="J109">
+        <v>0.68432183484381992</v>
+      </c>
+      <c r="K109">
+        <f t="shared" si="1"/>
+        <v>0.19199815212688393</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>45544</v>
       </c>
       <c r="B110">
-        <v>66.55</v>
+        <v>66.549999999999983</v>
       </c>
       <c r="C110">
         <v>205844.25</v>
@@ -16212,23 +15905,18 @@
       <c r="D110">
         <v>5086.8250000000007</v>
       </c>
-      <c r="E110">
-        <v>211.9510416666667</v>
-      </c>
-      <c r="F110">
-        <f t="shared" si="3"/>
-        <v>0.22483108108108107</v>
-      </c>
-      <c r="G110">
-        <f t="shared" si="4"/>
-        <v>0.74581249999999999</v>
-      </c>
-      <c r="H110">
-        <f t="shared" si="5"/>
-        <v>0.16768183065878378</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I110">
+        <v>0.22462239473462151</v>
+      </c>
+      <c r="J110">
+        <v>0.74383970773166808</v>
+      </c>
+      <c r="K110">
+        <f t="shared" si="1"/>
+        <v>0.16708305644938823</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>45551</v>
       </c>
@@ -16241,23 +15929,18 @@
       <c r="D111">
         <v>5268.2749999999996</v>
       </c>
-      <c r="E111">
-        <v>219.51145833333331</v>
-      </c>
-      <c r="F111">
-        <f t="shared" si="3"/>
-        <v>0.10608108108108108</v>
-      </c>
-      <c r="G111">
-        <f t="shared" si="4"/>
-        <v>0.79381068840579705</v>
-      </c>
-      <c r="H111">
-        <f t="shared" si="5"/>
-        <v>8.4208295999804145E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I111">
+        <v>0.10598261750063286</v>
+      </c>
+      <c r="J111">
+        <v>0.79171093332176967</v>
+      </c>
+      <c r="K111">
+        <f t="shared" si="1"/>
+        <v>8.3907597017310154E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>45558</v>
       </c>
@@ -16270,23 +15953,18 @@
       <c r="D112">
         <v>5123.3499999999995</v>
       </c>
-      <c r="E112">
-        <v>213.47291666666663</v>
-      </c>
-      <c r="F112">
-        <f t="shared" si="3"/>
-        <v>0.15532094594594595</v>
-      </c>
-      <c r="G112">
-        <f t="shared" si="4"/>
-        <v>0.82736050724637678</v>
-      </c>
-      <c r="H112">
-        <f t="shared" si="5"/>
-        <v>0.12850641662382492</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I112">
+        <v>0.15517677833094257</v>
+      </c>
+      <c r="J112">
+        <v>0.82517200757411491</v>
+      </c>
+      <c r="K112">
+        <f t="shared" si="1"/>
+        <v>0.12804753370422728</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>45565</v>
       </c>
@@ -16299,28 +15977,23 @@
       <c r="D113">
         <v>5553.6500000000005</v>
       </c>
-      <c r="E113">
-        <v>231.40208333333337</v>
-      </c>
-      <c r="F113">
-        <f t="shared" si="3"/>
-        <v>0.16613175675675676</v>
-      </c>
-      <c r="G113">
-        <f t="shared" si="4"/>
-        <v>0.84706793478260867</v>
-      </c>
-      <c r="H113">
-        <f t="shared" si="5"/>
-        <v>0.14072488409775263</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I113">
+        <v>0.16597755463673952</v>
+      </c>
+      <c r="J113">
+        <v>0.84482730584103027</v>
+      </c>
+      <c r="K113">
+        <f t="shared" si="1"/>
+        <v>0.14022237031383905</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>45572</v>
       </c>
       <c r="B114">
-        <v>76.524999999999991</v>
+        <v>76.525000000000006</v>
       </c>
       <c r="C114">
         <v>235176</v>
@@ -16328,28 +16001,23 @@
       <c r="D114">
         <v>5569.6750000000002</v>
       </c>
-      <c r="E114">
-        <v>232.06979166666667</v>
-      </c>
-      <c r="F114">
-        <f t="shared" si="3"/>
-        <v>0.25853040540540539</v>
-      </c>
-      <c r="G114">
-        <f t="shared" si="4"/>
-        <v>0.85208695652173905</v>
-      </c>
-      <c r="H114">
-        <f t="shared" si="5"/>
-        <v>0.22029038631022324</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I114">
+        <v>0.25829043962534809</v>
+      </c>
+      <c r="J114">
+        <v>0.84983305147218235</v>
+      </c>
+      <c r="K114">
+        <f t="shared" si="1"/>
+        <v>0.21950375247290105</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>45579</v>
       </c>
       <c r="B115">
-        <v>84.124999999999986</v>
+        <v>84.125</v>
       </c>
       <c r="C115">
         <v>244599</v>
@@ -16357,23 +16025,18 @@
       <c r="D115">
         <v>5783.0749999999998</v>
       </c>
-      <c r="E115">
-        <v>240.96145833333333</v>
-      </c>
-      <c r="F115">
-        <f t="shared" si="3"/>
-        <v>0.28420608108108103</v>
-      </c>
-      <c r="G115">
-        <f t="shared" si="4"/>
-        <v>0.88622826086956519</v>
-      </c>
-      <c r="H115">
-        <f t="shared" si="5"/>
-        <v>0.25187146096504109</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I115">
+        <v>0.28394228335161592</v>
+      </c>
+      <c r="J115">
+        <v>0.88388404665886111</v>
+      </c>
+      <c r="K115">
+        <f t="shared" si="1"/>
+        <v>0.25097205442638326</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>45586</v>
       </c>
@@ -16386,23 +16049,18 @@
       <c r="D116">
         <v>5916.0249999999996</v>
       </c>
-      <c r="E116">
-        <v>246.50104166666665</v>
-      </c>
-      <c r="F116">
-        <f t="shared" si="3"/>
-        <v>0.41824324324324325</v>
-      </c>
-      <c r="G116">
-        <f t="shared" si="4"/>
-        <v>0.90317300724637672</v>
-      </c>
-      <c r="H116">
-        <f t="shared" si="5"/>
-        <v>0.37774600776047784</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I116">
+        <v>0.41785503333052065</v>
+      </c>
+      <c r="J116">
+        <v>0.90078397149588763</v>
+      </c>
+      <c r="K116">
+        <f t="shared" si="1"/>
+        <v>0.37639711643301288</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>45593</v>
       </c>
@@ -16415,23 +16073,18 @@
       <c r="D117">
         <v>5906.1750000000002</v>
       </c>
-      <c r="E117">
-        <v>246.09062500000002</v>
-      </c>
-      <c r="F117">
-        <f t="shared" si="3"/>
-        <v>0.47829391891891887</v>
-      </c>
-      <c r="G117">
-        <f t="shared" si="4"/>
-        <v>0.89492119565217398</v>
-      </c>
-      <c r="H117">
-        <f t="shared" si="5"/>
-        <v>0.42803536579208284</v>
-      </c>
-    </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I117">
+        <v>0.47784997046662731</v>
+      </c>
+      <c r="J117">
+        <v>0.89255398725120327</v>
+      </c>
+      <c r="K117">
+        <f t="shared" si="1"/>
+        <v>0.42650689644785794</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>45600</v>
       </c>
@@ -16444,23 +16097,18 @@
       <c r="D118">
         <v>5821.15</v>
       </c>
-      <c r="E118">
-        <v>242.54791666666665</v>
-      </c>
-      <c r="F118">
-        <f t="shared" si="3"/>
-        <v>0.57981418918918914</v>
-      </c>
-      <c r="G118">
-        <f t="shared" si="4"/>
-        <v>0.88036322463768124</v>
-      </c>
-      <c r="H118">
-        <f t="shared" si="5"/>
-        <v>0.51044708928527716</v>
-      </c>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I118">
+        <v>0.57927601046325206</v>
+      </c>
+      <c r="J118">
+        <v>0.87803452437737595</v>
+      </c>
+      <c r="K118">
+        <f t="shared" si="1"/>
+        <v>0.50862433633032533</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>45607</v>
       </c>
@@ -16473,23 +16121,18 @@
       <c r="D119">
         <v>5701</v>
       </c>
-      <c r="E119">
-        <v>237.54166666666666</v>
-      </c>
-      <c r="F119">
-        <f t="shared" si="3"/>
-        <v>0.65396959459459458</v>
-      </c>
-      <c r="G119">
-        <f t="shared" si="4"/>
-        <v>0.83278442028985511</v>
-      </c>
-      <c r="H119">
-        <f t="shared" si="5"/>
-        <v>0.54461568972165098</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I119">
+        <v>0.65336258543582826</v>
+      </c>
+      <c r="J119">
+        <v>0.83058157350794259</v>
+      </c>
+      <c r="K119">
+        <f t="shared" si="1"/>
+        <v>0.54267092428250785</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>45614</v>
       </c>
@@ -16502,23 +16145,18 @@
       <c r="D120">
         <v>5791.0249999999996</v>
       </c>
-      <c r="E120">
-        <v>241.29270833333331</v>
-      </c>
-      <c r="F120">
-        <f t="shared" si="3"/>
-        <v>0.8904560810810811</v>
-      </c>
-      <c r="G120">
-        <f t="shared" si="4"/>
-        <v>0.81950362318840575</v>
-      </c>
-      <c r="H120">
-        <f t="shared" si="5"/>
-        <v>0.7297319847360948</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I120">
+        <v>0.88962956712513719</v>
+      </c>
+      <c r="J120">
+        <v>0.81733590621973595</v>
+      </c>
+      <c r="K120">
+        <f t="shared" si="1"/>
+        <v>0.72712618844609544</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>45621</v>
       </c>
@@ -16531,23 +16169,18 @@
       <c r="D121">
         <v>5716.8499999999995</v>
       </c>
-      <c r="E121">
-        <v>238.20208333333332</v>
-      </c>
-      <c r="F121">
-        <f t="shared" si="3"/>
-        <v>0.79636824324324318</v>
-      </c>
-      <c r="G121">
-        <f t="shared" si="4"/>
-        <v>0.82967844202898555</v>
-      </c>
-      <c r="H121">
-        <f t="shared" si="5"/>
-        <v>0.66072956333541422</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I121">
+        <v>0.79562906083874785</v>
+      </c>
+      <c r="J121">
+        <v>0.82748381105184798</v>
+      </c>
+      <c r="K121">
+        <f t="shared" si="1"/>
+        <v>0.65837016744644972</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>45628</v>
       </c>
@@ -16560,23 +16193,18 @@
       <c r="D122">
         <v>5802.5499999999993</v>
       </c>
-      <c r="E122">
-        <v>241.77291666666665</v>
-      </c>
-      <c r="F122">
-        <f t="shared" si="3"/>
-        <v>0.68167229729729728</v>
-      </c>
-      <c r="G122">
-        <f t="shared" si="4"/>
-        <v>0.8412608695652174</v>
-      </c>
-      <c r="H122">
-        <f t="shared" si="5"/>
-        <v>0.57346422958284371</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I122">
+        <v>0.68103957471943299</v>
+      </c>
+      <c r="J122">
+        <v>0.83903560123151633</v>
+      </c>
+      <c r="K122">
+        <f t="shared" si="1"/>
+        <v>0.5714164490371757</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>45635</v>
       </c>
@@ -16589,23 +16217,18 @@
       <c r="D123">
         <v>5548.8249999999998</v>
       </c>
-      <c r="E123">
-        <v>231.20104166666667</v>
-      </c>
-      <c r="F123">
-        <f t="shared" si="3"/>
-        <v>0.66055743243243248</v>
-      </c>
-      <c r="G123">
-        <f t="shared" si="4"/>
-        <v>0.84430615942028986</v>
-      </c>
-      <c r="H123">
-        <f t="shared" si="5"/>
-        <v>0.55771270885355473</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I123">
+        <v>0.65994430849717334</v>
+      </c>
+      <c r="J123">
+        <v>0.842072835812266</v>
+      </c>
+      <c r="K123">
+        <f t="shared" si="1"/>
+        <v>0.5557211753343797</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>45642</v>
       </c>
@@ -16618,23 +16241,18 @@
       <c r="D124">
         <v>5344.7749999999996</v>
       </c>
-      <c r="E124">
-        <v>222.69895833333331</v>
-      </c>
-      <c r="F124">
-        <f t="shared" si="3"/>
-        <v>0.61317567567567566</v>
-      </c>
-      <c r="G124">
-        <f t="shared" si="4"/>
-        <v>0.81622101449275353</v>
-      </c>
-      <c r="H124">
-        <f t="shared" si="5"/>
-        <v>0.5004868720622796</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I124">
+        <v>0.61260653109442242</v>
+      </c>
+      <c r="J124">
+        <v>0.8140619805443533</v>
+      </c>
+      <c r="K124">
+        <f t="shared" si="1"/>
+        <v>0.49869968599713149</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>45649</v>
       </c>
@@ -16647,23 +16265,18 @@
       <c r="D125">
         <v>5276.65</v>
       </c>
-      <c r="E125">
-        <v>219.86041666666665</v>
-      </c>
-      <c r="F125">
-        <f t="shared" si="3"/>
-        <v>0.57913851351351353</v>
-      </c>
-      <c r="G125">
-        <f t="shared" si="4"/>
-        <v>0.81472101449275358</v>
-      </c>
-      <c r="H125">
-        <f t="shared" si="5"/>
-        <v>0.471836317261555</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I125">
+        <v>0.57860096194413979</v>
+      </c>
+      <c r="J125">
+        <v>0.81256594828209239</v>
+      </c>
+      <c r="K125">
+        <f t="shared" si="1"/>
+        <v>0.47015143931907077</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>45656</v>
       </c>
@@ -16676,23 +16289,18 @@
       <c r="D126">
         <v>5173.2</v>
       </c>
-      <c r="E126">
-        <v>215.54999999999998</v>
-      </c>
-      <c r="F126">
-        <f t="shared" si="3"/>
-        <v>0.51655405405405408</v>
-      </c>
-      <c r="G126">
-        <f t="shared" si="4"/>
-        <v>0.80549818840579712</v>
-      </c>
-      <c r="H126">
-        <f t="shared" si="5"/>
-        <v>0.41608335475421077</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I126">
+        <v>0.51607459286136192</v>
+      </c>
+      <c r="J126">
+        <v>0.80336751803188633</v>
+      </c>
+      <c r="K126">
+        <f t="shared" si="1"/>
+        <v>0.41459756478634857</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>45663</v>
       </c>
@@ -16705,28 +16313,23 @@
       <c r="D127">
         <v>5171.2249999999995</v>
       </c>
-      <c r="E127">
-        <v>215.46770833333332</v>
-      </c>
-      <c r="F127">
-        <f t="shared" si="3"/>
-        <v>0.45168918918918916</v>
-      </c>
-      <c r="G127">
-        <f t="shared" si="4"/>
-        <v>0.84702355072463775</v>
-      </c>
-      <c r="H127">
-        <f t="shared" si="5"/>
-        <v>0.38259138085095967</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I127">
+        <v>0.45126993502658003</v>
+      </c>
+      <c r="J127">
+        <v>0.84478303918592712</v>
+      </c>
+      <c r="K127">
+        <f t="shared" si="1"/>
+        <v>0.38122518720499016</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>45670</v>
       </c>
       <c r="B128">
-        <v>75.774999999999991</v>
+        <v>75.775000000000006</v>
       </c>
       <c r="C128">
         <v>248792.75</v>
@@ -16734,23 +16337,18 @@
       <c r="D128">
         <v>4964.2249999999995</v>
       </c>
-      <c r="E128">
-        <v>206.84270833333332</v>
-      </c>
-      <c r="F128">
-        <f t="shared" si="3"/>
-        <v>0.25599662162162157</v>
-      </c>
-      <c r="G128">
-        <f t="shared" si="4"/>
-        <v>0.90142300724637681</v>
-      </c>
-      <c r="H128">
-        <f t="shared" si="5"/>
-        <v>0.23076124450707497</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I128">
+        <v>0.25575900767867693</v>
+      </c>
+      <c r="J128">
+        <v>0.89903860052324991</v>
+      </c>
+      <c r="K128">
+        <f t="shared" si="1"/>
+        <v>0.22993722033465283</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>45677</v>
       </c>
@@ -16763,23 +16361,18 @@
       <c r="D129">
         <v>4870.1000000000004</v>
       </c>
-      <c r="E129">
-        <v>202.92083333333335</v>
-      </c>
-      <c r="F129">
-        <f t="shared" si="3"/>
-        <v>0.11275337837837837</v>
-      </c>
-      <c r="G129">
-        <f t="shared" si="4"/>
-        <v>0.93241666666666656</v>
-      </c>
-      <c r="H129">
-        <f t="shared" si="5"/>
-        <v>0.10513312922297295</v>
-      </c>
-    </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I129">
+        <v>0.11264872162686694</v>
+      </c>
+      <c r="J129">
+        <v>0.9299502768021044</v>
+      </c>
+      <c r="K129">
+        <f t="shared" si="1"/>
+        <v>0.10475770985830811</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>45684</v>
       </c>
@@ -16792,23 +16385,18 @@
       <c r="D130">
         <v>4714.3</v>
       </c>
-      <c r="E130">
-        <v>196.42916666666667</v>
-      </c>
-      <c r="F130">
-        <f t="shared" si="3"/>
-        <v>0.10903716216216215</v>
-      </c>
-      <c r="G130">
-        <f t="shared" si="4"/>
-        <v>0.93716213768115941</v>
-      </c>
-      <c r="H130">
-        <f t="shared" si="5"/>
-        <v>0.10218549997857911</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I130">
+        <v>0.10893595477174922</v>
+      </c>
+      <c r="J130">
+        <v>0.93468319529364141</v>
+      </c>
+      <c r="K130">
+        <f t="shared" si="1"/>
+        <v>0.10182060628842217</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>45691</v>
       </c>
@@ -16821,23 +16409,18 @@
       <c r="D131">
         <v>4964.2750000000005</v>
       </c>
-      <c r="E131">
-        <v>206.84479166666668</v>
-      </c>
-      <c r="F131">
-        <f t="shared" ref="F131:F155" si="6">B131/296</f>
-        <v>0.20135135135135135</v>
-      </c>
-      <c r="G131">
-        <f t="shared" ref="G131:G155" si="7">(C131/1000)/276</f>
-        <v>0.91860144927536225</v>
-      </c>
-      <c r="H131">
-        <f t="shared" ref="H131:H155" si="8">F131*G131</f>
-        <v>0.18496164316490402</v>
-      </c>
-    </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I131">
+        <v>0.20116445869546876</v>
+      </c>
+      <c r="J131">
+        <v>0.9161716028504111</v>
+      </c>
+      <c r="K131">
+        <f t="shared" ref="K131:K157" si="2">I131*J131</f>
+        <v>0.18430116455956294</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>45698</v>
       </c>
@@ -16850,23 +16433,18 @@
       <c r="D132">
         <v>5049.2250000000004</v>
       </c>
-      <c r="E132">
-        <v>210.38437500000001</v>
-      </c>
-      <c r="F132">
-        <f t="shared" si="6"/>
-        <v>0.35532094594594593</v>
-      </c>
-      <c r="G132">
-        <f t="shared" si="7"/>
-        <v>0.90345742753623193</v>
-      </c>
-      <c r="H132">
-        <f t="shared" si="8"/>
-        <v>0.32101734777406482</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I132">
+        <v>0.35499113998818665</v>
+      </c>
+      <c r="J132">
+        <v>0.90106763944899748</v>
+      </c>
+      <c r="K132">
+        <f t="shared" si="2"/>
+        <v>0.31987102853446397</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>45705</v>
       </c>
@@ -16879,23 +16457,18 @@
       <c r="D133">
         <v>5030.6000000000004</v>
       </c>
-      <c r="E133">
-        <v>209.60833333333335</v>
-      </c>
-      <c r="F133">
-        <f t="shared" si="6"/>
-        <v>0.38505067567567564</v>
-      </c>
-      <c r="G133">
-        <f t="shared" si="7"/>
-        <v>0.89321648550724642</v>
-      </c>
-      <c r="H133">
-        <f t="shared" si="8"/>
-        <v>0.34393361126921757</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I133">
+        <v>0.38469327482912835</v>
+      </c>
+      <c r="J133">
+        <v>0.89085378633479317</v>
+      </c>
+      <c r="K133">
+        <f t="shared" si="2"/>
+        <v>0.3427054604590602</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>45712</v>
       </c>
@@ -16908,23 +16481,18 @@
       <c r="D134">
         <v>5293.9250000000002</v>
       </c>
-      <c r="E134">
-        <v>220.58020833333333</v>
-      </c>
-      <c r="F134">
-        <f t="shared" si="6"/>
-        <v>0.33682432432432435</v>
-      </c>
-      <c r="G134">
-        <f t="shared" si="7"/>
-        <v>0.88492119565217386</v>
-      </c>
-      <c r="H134">
-        <f t="shared" si="8"/>
-        <v>0.29806298380581669</v>
-      </c>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I134">
+        <v>0.33651168677748716</v>
+      </c>
+      <c r="J134">
+        <v>0.88258043883613013</v>
+      </c>
+      <c r="K134">
+        <f t="shared" si="2"/>
+        <v>0.29699863218956096</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>45719</v>
       </c>
@@ -16937,23 +16505,18 @@
       <c r="D135">
         <v>5246.9500000000007</v>
       </c>
-      <c r="E135">
-        <v>218.6229166666667</v>
-      </c>
-      <c r="F135">
-        <f t="shared" si="6"/>
-        <v>0.42077702702702702</v>
-      </c>
-      <c r="G135">
-        <f t="shared" si="7"/>
-        <v>0.88699637681159427</v>
-      </c>
-      <c r="H135">
-        <f t="shared" si="8"/>
-        <v>0.37322769841852727</v>
-      </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I135">
+        <v>0.42038646527719181</v>
+      </c>
+      <c r="J135">
+        <v>0.88465013081248278</v>
+      </c>
+      <c r="K135">
+        <f t="shared" si="2"/>
+        <v>0.371894941499265</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>45726</v>
       </c>
@@ -16966,23 +16529,18 @@
       <c r="D136">
         <v>5479.2749999999996</v>
       </c>
-      <c r="E136">
-        <v>228.30312499999999</v>
-      </c>
-      <c r="F136">
-        <f t="shared" si="6"/>
-        <v>0.51469594594594592</v>
-      </c>
-      <c r="G136">
-        <f t="shared" si="7"/>
-        <v>0.84866032608695652</v>
-      </c>
-      <c r="H136">
-        <f t="shared" si="8"/>
-        <v>0.43680202932212103</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I136">
+        <v>0.51421820943380303</v>
+      </c>
+      <c r="J136">
+        <v>0.84641548501799568</v>
+      </c>
+      <c r="K136">
+        <f t="shared" si="2"/>
+        <v>0.43524225514299769</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>45733</v>
       </c>
@@ -16995,23 +16553,18 @@
       <c r="D137">
         <v>5669.625</v>
       </c>
-      <c r="E137">
-        <v>236.234375</v>
-      </c>
-      <c r="F137">
-        <f t="shared" si="6"/>
-        <v>0.58369932432432436</v>
-      </c>
-      <c r="G137">
-        <f t="shared" si="7"/>
-        <v>0.77921376811594201</v>
-      </c>
-      <c r="H137">
-        <f t="shared" si="8"/>
-        <v>0.45482654995348609</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I137">
+        <v>0.58315753944814785</v>
+      </c>
+      <c r="J137">
+        <v>0.77715262419958653</v>
+      </c>
+      <c r="K137">
+        <f t="shared" si="2"/>
+        <v>0.453202412103902</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>45740</v>
       </c>
@@ -17024,23 +16577,18 @@
       <c r="D138">
         <v>5749.0749999999998</v>
       </c>
-      <c r="E138">
-        <v>239.54479166666667</v>
-      </c>
-      <c r="F138">
-        <f t="shared" si="6"/>
-        <v>0.64940878378378375</v>
-      </c>
-      <c r="G138">
-        <f t="shared" si="7"/>
-        <v>0.79377355072463773</v>
-      </c>
-      <c r="H138">
-        <f t="shared" si="8"/>
-        <v>0.51548351617582255</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I138">
+        <v>0.64880600793182008</v>
+      </c>
+      <c r="J138">
+        <v>0.791673893875663</v>
+      </c>
+      <c r="K138">
+        <f t="shared" si="2"/>
+        <v>0.5136427786693083</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>45747</v>
       </c>
@@ -17053,23 +16601,18 @@
       <c r="D139">
         <v>5697.8499999999995</v>
       </c>
-      <c r="E139">
-        <v>237.41041666666663</v>
-      </c>
-      <c r="F139">
-        <f t="shared" si="6"/>
-        <v>0.67736486486486491</v>
-      </c>
-      <c r="G139">
-        <f t="shared" si="7"/>
-        <v>0.78300724637681163</v>
-      </c>
-      <c r="H139">
-        <f t="shared" si="8"/>
-        <v>0.53038159763023895</v>
-      </c>
-    </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I139">
+        <v>0.676736140410092</v>
+      </c>
+      <c r="J139">
+        <v>0.78093606810921756</v>
+      </c>
+      <c r="K139">
+        <f t="shared" si="2"/>
+        <v>0.52848766063926467</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>45754</v>
       </c>
@@ -17082,23 +16625,18 @@
       <c r="D140">
         <v>5724</v>
       </c>
-      <c r="E140">
-        <v>238.5</v>
-      </c>
-      <c r="F140">
-        <f t="shared" si="6"/>
-        <v>0.65194256756756752</v>
-      </c>
-      <c r="G140">
-        <f t="shared" si="7"/>
-        <v>0.7943786231884058</v>
-      </c>
-      <c r="H140">
-        <f t="shared" si="8"/>
-        <v>0.51788923922223851</v>
-      </c>
-    </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I140">
+        <v>0.65133743987849124</v>
+      </c>
+      <c r="J140">
+        <v>0.79227736582686492</v>
+      </c>
+      <c r="K140">
+        <f t="shared" si="2"/>
+        <v>0.51603991113134506</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>45761</v>
       </c>
@@ -17111,23 +16649,18 @@
       <c r="D141">
         <v>5810.5999999999995</v>
       </c>
-      <c r="E141">
-        <v>242.10833333333332</v>
-      </c>
-      <c r="F141">
-        <f t="shared" si="6"/>
-        <v>0.5868243243243243</v>
-      </c>
-      <c r="G141">
-        <f t="shared" si="7"/>
-        <v>0.81058514492753619</v>
-      </c>
-      <c r="H141">
-        <f t="shared" si="8"/>
-        <v>0.47567107997943592</v>
-      </c>
-    </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I141">
+        <v>0.58627963884904233</v>
+      </c>
+      <c r="J141">
+        <v>0.80844101874738006</v>
+      </c>
+      <c r="K141">
+        <f t="shared" si="2"/>
+        <v>0.47397250850196582</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>45768</v>
       </c>
@@ -17140,23 +16673,18 @@
       <c r="D142">
         <v>5675.2</v>
       </c>
-      <c r="E142">
-        <v>236.46666666666667</v>
-      </c>
-      <c r="F142">
-        <f t="shared" si="6"/>
-        <v>0.91528716216216222</v>
-      </c>
-      <c r="G142">
-        <f t="shared" si="7"/>
-        <v>0.82074365942028982</v>
-      </c>
-      <c r="H142">
-        <f t="shared" si="8"/>
-        <v>0.75121613489338523</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I142">
+        <v>0.91443760020251463</v>
+      </c>
+      <c r="J142">
+        <v>0.81857266235924997</v>
+      </c>
+      <c r="K142">
+        <f t="shared" si="2"/>
+        <v>0.74853362095917586</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>45775</v>
       </c>
@@ -17169,23 +16697,18 @@
       <c r="D143">
         <v>5766.7999999999993</v>
       </c>
-      <c r="E143">
-        <v>240.2833333333333</v>
-      </c>
-      <c r="F143">
-        <f t="shared" si="6"/>
-        <v>1.0009290540540541</v>
-      </c>
-      <c r="G143">
-        <f t="shared" si="7"/>
-        <v>0.81923550724637684</v>
-      </c>
-      <c r="H143">
-        <f t="shared" si="8"/>
-        <v>0.81999662131560913</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="J143">
+        <v>0.81706849948686811</v>
+      </c>
+      <c r="K143">
+        <f t="shared" si="2"/>
+        <v>0.81706849948686811</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>45782</v>
       </c>
@@ -17198,23 +16721,18 @@
       <c r="D144">
         <v>5651</v>
       </c>
-      <c r="E144">
-        <v>235.45833333333334</v>
-      </c>
-      <c r="F144">
-        <f t="shared" si="6"/>
-        <v>0.88581081081081081</v>
-      </c>
-      <c r="G144">
-        <f t="shared" si="7"/>
-        <v>0.79534510869565223</v>
-      </c>
-      <c r="H144">
-        <f t="shared" si="8"/>
-        <v>0.70452529560810817</v>
-      </c>
-    </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I144">
+        <v>0.88498860855624006</v>
+      </c>
+      <c r="J144">
+        <v>0.79324129482676375</v>
+      </c>
+      <c r="K144">
+        <f t="shared" si="2"/>
+        <v>0.70200950975808785</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>45789</v>
       </c>
@@ -17227,23 +16745,18 @@
       <c r="D145">
         <v>5712.0749999999998</v>
       </c>
-      <c r="E145">
-        <v>238.00312499999998</v>
-      </c>
-      <c r="F145">
-        <f t="shared" si="6"/>
-        <v>0.8439189189189189</v>
-      </c>
-      <c r="G145">
-        <f t="shared" si="7"/>
-        <v>0.77807608695652175</v>
-      </c>
-      <c r="H145">
-        <f t="shared" si="8"/>
-        <v>0.65663313014101055</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I145">
+        <v>0.84313560037127677</v>
+      </c>
+      <c r="J145">
+        <v>0.77601795238714699</v>
+      </c>
+      <c r="K145">
+        <f t="shared" si="2"/>
+        <v>0.654288362184826</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>45796</v>
       </c>
@@ -17256,23 +16769,18 @@
       <c r="D146">
         <v>5749.2750000000005</v>
       </c>
-      <c r="E146">
-        <v>239.55312500000002</v>
-      </c>
-      <c r="F146">
-        <f t="shared" si="6"/>
-        <v>0.89957770270270265</v>
-      </c>
-      <c r="G146">
-        <f t="shared" si="7"/>
-        <v>0.75641485507246375</v>
-      </c>
-      <c r="H146">
-        <f t="shared" si="8"/>
-        <v>0.6804539376162847</v>
-      </c>
-    </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I146">
+        <v>0.89874272213315332</v>
+      </c>
+      <c r="J146">
+        <v>0.75441401789456941</v>
+      </c>
+      <c r="K146">
+        <f t="shared" si="2"/>
+        <v>0.67802410805797475</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>45803</v>
       </c>
@@ -17285,23 +16793,18 @@
       <c r="D147">
         <v>5727.95</v>
       </c>
-      <c r="E147">
-        <v>238.66458333333333</v>
-      </c>
-      <c r="F147">
-        <f t="shared" si="6"/>
-        <v>0.85152027027027033</v>
-      </c>
-      <c r="G147">
-        <f t="shared" si="7"/>
-        <v>0.75115398550724632</v>
-      </c>
-      <c r="H147">
-        <f t="shared" si="8"/>
-        <v>0.63962284475372111</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I147">
+        <v>0.85072989621129025</v>
+      </c>
+      <c r="J147">
+        <v>0.74916706416316137</v>
+      </c>
+      <c r="K147">
+        <f t="shared" si="2"/>
+        <v>0.63733881874044329</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>45810</v>
       </c>
@@ -17314,23 +16817,18 @@
       <c r="D148">
         <v>5674.65</v>
       </c>
-      <c r="E148">
-        <v>236.44374999999999</v>
-      </c>
-      <c r="F148">
-        <f t="shared" si="6"/>
-        <v>0.72415540540540535</v>
-      </c>
-      <c r="G148">
-        <f t="shared" si="7"/>
-        <v>0.74334601449275362</v>
-      </c>
-      <c r="H148">
-        <f t="shared" si="8"/>
-        <v>0.53829803448149227</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I148">
+        <v>0.7234832503586196</v>
+      </c>
+      <c r="J148">
+        <v>0.74137974646950833</v>
+      </c>
+      <c r="K148">
+        <f t="shared" si="2"/>
+        <v>0.53637582872580924</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>45817</v>
       </c>
@@ -17343,23 +16841,18 @@
       <c r="D149">
         <v>5533.0250000000005</v>
       </c>
-      <c r="E149">
-        <v>230.54270833333337</v>
-      </c>
-      <c r="F149">
-        <f t="shared" si="6"/>
-        <v>0.80540540540540539</v>
-      </c>
-      <c r="G149">
-        <f t="shared" si="7"/>
-        <v>0.70840036231884052</v>
-      </c>
-      <c r="H149">
-        <f t="shared" si="8"/>
-        <v>0.57054948100274183</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I149">
+        <v>0.80465783478187503</v>
+      </c>
+      <c r="J149">
+        <v>0.70652653108422581</v>
+      </c>
+      <c r="K149">
+        <f t="shared" si="2"/>
+        <v>0.56851210871818225</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>45824</v>
       </c>
@@ -17372,23 +16865,18 @@
       <c r="D150">
         <v>5449.2249999999995</v>
       </c>
-      <c r="E150">
-        <v>227.05104166666663</v>
-      </c>
-      <c r="F150">
-        <f t="shared" si="6"/>
-        <v>0.73699324324324322</v>
-      </c>
-      <c r="G150">
-        <f t="shared" si="7"/>
-        <v>0.68918025362318847</v>
-      </c>
-      <c r="H150">
-        <f t="shared" si="8"/>
-        <v>0.50792119029695459</v>
-      </c>
-    </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I150">
+        <v>0.73630917222175352</v>
+      </c>
+      <c r="J150">
+        <v>0.68735726262232044</v>
+      </c>
+      <c r="K150">
+        <f t="shared" si="2"/>
+        <v>0.50610745706205118</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>45831</v>
       </c>
@@ -17401,23 +16889,18 @@
       <c r="D151">
         <v>5359.35</v>
       </c>
-      <c r="E151">
-        <v>223.30625000000001</v>
-      </c>
-      <c r="F151">
-        <f t="shared" si="6"/>
-        <v>0.53158783783783781</v>
-      </c>
-      <c r="G151">
-        <f t="shared" si="7"/>
-        <v>0.68825815217391306</v>
-      </c>
-      <c r="H151">
-        <f t="shared" si="8"/>
-        <v>0.36586966298839602</v>
-      </c>
-    </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I151">
+        <v>0.53109442241161087</v>
+      </c>
+      <c r="J151">
+        <v>0.68643760027752476</v>
+      </c>
+      <c r="K151">
+        <f t="shared" si="2"/>
+        <v>0.36456318084100425</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>45838</v>
       </c>
@@ -17430,23 +16913,18 @@
       <c r="D152">
         <v>5280.4499999999989</v>
       </c>
-      <c r="E152">
-        <v>220.01874999999995</v>
-      </c>
-      <c r="F152">
-        <f t="shared" si="6"/>
-        <v>0.47483108108108113</v>
-      </c>
-      <c r="G152">
-        <f t="shared" si="7"/>
-        <v>0.68172463768115943</v>
-      </c>
-      <c r="H152">
-        <f t="shared" si="8"/>
-        <v>0.32370404670975328</v>
-      </c>
-    </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I152">
+        <v>0.47439034680617675</v>
+      </c>
+      <c r="J152">
+        <v>0.67992136796611879</v>
+      </c>
+      <c r="K152">
+        <f t="shared" si="2"/>
+        <v>0.3225481335503772</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>45845</v>
       </c>
@@ -17459,23 +16937,18 @@
       <c r="D153">
         <v>5143.4249999999993</v>
       </c>
-      <c r="E153">
-        <v>214.30937499999996</v>
-      </c>
-      <c r="F153">
-        <f t="shared" si="6"/>
-        <v>0.47972972972972971</v>
-      </c>
-      <c r="G153">
-        <f t="shared" si="7"/>
-        <v>0.68871829710144927</v>
-      </c>
-      <c r="H153">
-        <f t="shared" si="8"/>
-        <v>0.33039864252839796</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I153">
+        <v>0.47928444856974101</v>
+      </c>
+      <c r="J153">
+        <v>0.68689652804879808</v>
+      </c>
+      <c r="K153">
+        <f t="shared" si="2"/>
+        <v>0.32921882367033783</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>45852</v>
       </c>
@@ -17488,67 +16961,87 @@
       <c r="D154">
         <v>4985.8499999999995</v>
       </c>
-      <c r="E154">
-        <v>207.74374999999998</v>
-      </c>
-      <c r="F154">
-        <f t="shared" si="6"/>
-        <v>0.3904560810810811</v>
-      </c>
-      <c r="G154">
-        <f t="shared" si="7"/>
-        <v>0.69643931159420291</v>
-      </c>
-      <c r="H154">
-        <f t="shared" si="8"/>
-        <v>0.27192896431587837</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I154">
+        <v>0.39009366298202686</v>
+      </c>
+      <c r="J154">
+        <v>0.69459711923449396</v>
+      </c>
+      <c r="K154">
+        <f t="shared" si="2"/>
+        <v>0.2709579345389474</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>45859</v>
       </c>
       <c r="B155">
-        <v>121.175</v>
+        <v>116.72499999999999</v>
       </c>
       <c r="C155">
-        <v>192302</v>
+        <v>195892.75</v>
       </c>
       <c r="D155">
-        <v>4440.6500000000005</v>
-      </c>
-      <c r="E155">
-        <v>185.02708333333337</v>
-      </c>
-      <c r="F155">
-        <f t="shared" si="6"/>
-        <v>0.40937499999999999</v>
-      </c>
-      <c r="G155">
-        <f t="shared" si="7"/>
-        <v>0.69674637681159413</v>
-      </c>
-      <c r="H155">
-        <f t="shared" si="8"/>
-        <v>0.28523054800724634</v>
-      </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+        <v>4970.2</v>
+      </c>
+      <c r="I155">
+        <v>0.39397519196692266</v>
+      </c>
+      <c r="J155">
+        <v>0.70787892256768281</v>
+      </c>
+      <c r="K155">
+        <f t="shared" si="2"/>
+        <v>0.27888673440794121</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" s="2">
+        <v>45866</v>
+      </c>
       <c r="B156">
-        <f>MAX(B2:B155)</f>
-        <v>296.27499999999998</v>
+        <v>128.15</v>
       </c>
       <c r="C156">
-        <f t="shared" ref="C156:E156" si="9">MAX(C2:C155)</f>
-        <v>276732</v>
+        <v>195189</v>
       </c>
       <c r="D156">
-        <f t="shared" si="9"/>
-        <v>6896.7749999999996</v>
-      </c>
-      <c r="E156">
-        <f t="shared" si="9"/>
-        <v>287.36562499999997</v>
+        <v>4885.55</v>
+      </c>
+      <c r="I156">
+        <v>0.43253733862121346</v>
+      </c>
+      <c r="J156">
+        <v>0.70533584840206398</v>
+      </c>
+      <c r="K156">
+        <f t="shared" si="2"/>
+        <v>0.30508409070196441</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" s="2">
+        <v>45873</v>
+      </c>
+      <c r="B157">
+        <v>153.85</v>
+      </c>
+      <c r="C157">
+        <v>195350.25</v>
+      </c>
+      <c r="D157">
+        <v>4707.0249999999996</v>
+      </c>
+      <c r="I157">
+        <v>0.51928107332714546</v>
+      </c>
+      <c r="J157">
+        <v>0.70591854212740113</v>
+      </c>
+      <c r="K157">
+        <f t="shared" si="2"/>
+        <v>0.3665701382374506</v>
       </c>
     </row>
   </sheetData>
